--- a/Onsite/submissions.xlsx
+++ b/Onsite/submissions.xlsx
@@ -10,8 +10,6 @@
     <sheet name="All (with win-rate)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Top by win-rate (≥5k)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SFT progress" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Legend" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All (with win-rate)'!$A$1:$W$1</definedName>
@@ -38,12 +36,12 @@
       <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -101,32 +99,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,14 +489,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:W48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
@@ -783,13 +780,13 @@
         </is>
       </c>
       <c r="K3" s="4" t="n">
-        <v>5789</v>
+        <v>7828</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1527</v>
+        <v>2087</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.2638</v>
+        <v>0.2666</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
@@ -881,13 +878,13 @@
         </is>
       </c>
       <c r="K4" s="4" t="n">
-        <v>5786</v>
+        <v>7787</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1559</v>
+        <v>2129</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.2694</v>
+        <v>0.2734</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
@@ -979,13 +976,13 @@
         </is>
       </c>
       <c r="K5" s="4" t="n">
-        <v>5853</v>
+        <v>7854</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1865</v>
+        <v>2508</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3186</v>
+        <v>0.3193</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1077,13 +1074,13 @@
         </is>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5748</v>
+        <v>7786</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1135</v>
+        <v>1527</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1975</v>
+        <v>0.1961</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -1175,13 +1172,13 @@
         </is>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5771</v>
+        <v>7804</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1434</v>
+        <v>1945</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2485</v>
+        <v>0.2492</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
@@ -1273,13 +1270,13 @@
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5811</v>
+        <v>7852</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1738</v>
+        <v>2378</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.2991</v>
+        <v>0.3029</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
@@ -1371,13 +1368,13 @@
         </is>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5803</v>
+        <v>7827</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1727</v>
+        <v>2299</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2976</v>
+        <v>0.2937</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
@@ -1469,13 +1466,13 @@
         </is>
       </c>
       <c r="K10" s="7" t="n">
-        <v>5699</v>
+        <v>7719</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>1961</v>
+        <v>2661</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>0.3441</v>
+        <v>0.3447</v>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
@@ -1567,13 +1564,13 @@
         </is>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5667</v>
+        <v>7681</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1664</v>
+        <v>2278</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2936</v>
+        <v>0.2966</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -2166,13 +2163,13 @@
         </is>
       </c>
       <c r="K18" s="10" t="n">
-        <v>1455</v>
+        <v>3506</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>480</v>
+        <v>1184</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3299</v>
+        <v>0.3377</v>
       </c>
       <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" s="10" t="inlineStr">
@@ -2263,13 +2260,13 @@
         </is>
       </c>
       <c r="K19" s="10" t="n">
-        <v>5510</v>
+        <v>7612</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>1804</v>
+        <v>2505</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.3274</v>
+        <v>0.3291</v>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
@@ -2364,13 +2361,13 @@
         </is>
       </c>
       <c r="K20" s="10" t="n">
-        <v>5439</v>
+        <v>7497</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>1762</v>
+        <v>2421</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.324</v>
+        <v>0.3229</v>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
@@ -2462,13 +2459,13 @@
         </is>
       </c>
       <c r="K21" s="10" t="n">
-        <v>5597</v>
+        <v>7602</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>1784</v>
+        <v>2398</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.3187</v>
+        <v>0.3154</v>
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
@@ -2560,13 +2557,13 @@
         </is>
       </c>
       <c r="K22" s="10" t="n">
-        <v>5653</v>
+        <v>7744</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>1729</v>
+        <v>2376</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.3059</v>
+        <v>0.3068</v>
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
@@ -2658,13 +2655,13 @@
         </is>
       </c>
       <c r="K23" s="10" t="n">
-        <v>5579</v>
+        <v>7559</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>1604</v>
+        <v>2203</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.2875</v>
+        <v>0.2914</v>
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
@@ -2756,13 +2753,13 @@
         </is>
       </c>
       <c r="K24" s="10" t="n">
-        <v>1440</v>
+        <v>3439</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>554</v>
+        <v>1322</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.3847</v>
+        <v>0.3844</v>
       </c>
       <c r="N24" s="10" t="inlineStr"/>
       <c r="O24" s="10" t="inlineStr">
@@ -2853,13 +2850,13 @@
         </is>
       </c>
       <c r="K25" s="7" t="n">
-        <v>5363</v>
+        <v>7314</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>1923</v>
+        <v>2636</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.3586</v>
+        <v>0.3604</v>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
@@ -3142,13 +3139,13 @@
         </is>
       </c>
       <c r="K28" s="7" t="n">
-        <v>5434</v>
+        <v>7496</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>1912</v>
+        <v>2640</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>0.3519</v>
+        <v>0.3522</v>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
@@ -3243,13 +3240,13 @@
         </is>
       </c>
       <c r="K29" s="10" t="n">
-        <v>1435</v>
+        <v>3411</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>483</v>
+        <v>1150</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.3366</v>
+        <v>0.3371</v>
       </c>
       <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" s="10" t="inlineStr">
@@ -3340,13 +3337,13 @@
         </is>
       </c>
       <c r="K30" s="10" t="n">
-        <v>5644</v>
+        <v>7659</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>1761</v>
+        <v>2443</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.312</v>
+        <v>0.319</v>
       </c>
       <c r="N30" s="10" t="inlineStr">
         <is>
@@ -3438,13 +3435,13 @@
         </is>
       </c>
       <c r="K31" s="10" t="n">
-        <v>5704</v>
+        <v>7686</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>1637</v>
+        <v>2195</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.287</v>
+        <v>0.2856</v>
       </c>
       <c r="N31" s="10" t="inlineStr">
         <is>
@@ -3561,13 +3558,13 @@
         </is>
       </c>
       <c r="K33" s="13" t="n">
-        <v>1380</v>
+        <v>3367</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>397</v>
+        <v>975</v>
       </c>
       <c r="M33" s="15" t="n">
-        <v>0.2877</v>
+        <v>0.2896</v>
       </c>
       <c r="N33" s="13" t="inlineStr"/>
       <c r="O33" s="13" t="inlineStr">
@@ -3655,13 +3652,13 @@
         </is>
       </c>
       <c r="K34" s="13" t="n">
-        <v>1397</v>
+        <v>3445</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>380</v>
+        <v>932</v>
       </c>
       <c r="M34" s="15" t="n">
-        <v>0.272</v>
+        <v>0.2705</v>
       </c>
       <c r="N34" s="13" t="inlineStr"/>
       <c r="O34" s="13" t="inlineStr">
@@ -3843,13 +3840,13 @@
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>545</v>
+        <v>2609</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>175</v>
+        <v>781</v>
       </c>
       <c r="M36" s="15" t="n">
-        <v>0.3211</v>
+        <v>0.2993</v>
       </c>
       <c r="N36" s="13" t="inlineStr"/>
       <c r="O36" s="13" t="inlineStr">
@@ -3913,22 +3910,22 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>B: +CoSER guide</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200</t>
+          <t>qwen3b_coser_step200_coser_guide</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v1</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v3</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v3</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr">
@@ -3937,13 +3934,13 @@
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>584</v>
+        <v>2683</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>159</v>
+        <v>723</v>
       </c>
       <c r="M37" s="15" t="n">
-        <v>0.2723</v>
+        <v>0.2695</v>
       </c>
       <c r="N37" s="13" t="inlineStr"/>
       <c r="O37" s="13" t="inlineStr">
@@ -3975,7 +3972,7 @@
       <c r="V37" s="13" t="inlineStr"/>
       <c r="W37" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T21:17:00</t>
+          <t>2026-06-19T21:17:04</t>
         </is>
       </c>
     </row>
@@ -4007,22 +4004,22 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>B: +CoSER guide</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200_coser_guide</t>
+          <t>qwen3b_coser_step200</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v3</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v1</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v3</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v1</t>
         </is>
       </c>
       <c r="J38" s="13" t="inlineStr">
@@ -4031,13 +4028,13 @@
         </is>
       </c>
       <c r="K38" s="13" t="n">
-        <v>571</v>
+        <v>2571</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>151</v>
+        <v>670</v>
       </c>
       <c r="M38" s="15" t="n">
-        <v>0.2644</v>
+        <v>0.2606</v>
       </c>
       <c r="N38" s="13" t="inlineStr"/>
       <c r="O38" s="13" t="inlineStr">
@@ -4069,7 +4066,7 @@
       <c r="V38" s="13" t="inlineStr"/>
       <c r="W38" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T21:17:04</t>
+          <t>2026-06-19T21:17:00</t>
         </is>
       </c>
     </row>
@@ -4125,13 +4122,13 @@
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>303</v>
+        <v>2457</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>83</v>
+        <v>709</v>
       </c>
       <c r="M39" s="15" t="n">
-        <v>0.2739</v>
+        <v>0.2886</v>
       </c>
       <c r="N39" s="13" t="inlineStr"/>
       <c r="O39" s="13" t="inlineStr">
@@ -4219,13 +4216,13 @@
         </is>
       </c>
       <c r="K40" s="13" t="n">
-        <v>285</v>
+        <v>2399</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>73</v>
+        <v>666</v>
       </c>
       <c r="M40" s="15" t="n">
-        <v>0.2561</v>
+        <v>0.2776</v>
       </c>
       <c r="N40" s="13" t="inlineStr"/>
       <c r="O40" s="13" t="inlineStr">
@@ -4313,13 +4310,13 @@
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>305</v>
+        <v>2327</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>74</v>
+        <v>572</v>
       </c>
       <c r="M41" s="15" t="n">
-        <v>0.2426</v>
+        <v>0.2458</v>
       </c>
       <c r="N41" s="13" t="inlineStr"/>
       <c r="O41" s="13" t="inlineStr">
@@ -4352,6 +4349,664 @@
       <c r="W41" s="13" t="inlineStr">
         <is>
           <t>2026-06-19T21:24:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Qwen2.5</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>SFT-PIPPA-r32</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>C: best_of=16</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>qwen3b_pippa_r32_bo16</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen2.5-3B-PIPPA-r32</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>793</v>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>242</v>
+      </c>
+      <c r="M42" s="15" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="N42" s="13" t="inlineStr"/>
+      <c r="O42" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="S42" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T42" s="13" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="U42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="13" t="inlineStr"/>
+      <c r="W42" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:11:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>Qwen2.5</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>SFT-PIPPA-r32</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>qwen3b_pippa_r32</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen2.5-3B-PIPPA-r32</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>773</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>213</v>
+      </c>
+      <c r="M43" s="15" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="N43" s="13" t="inlineStr"/>
+      <c r="O43" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S43" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T43" s="13" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="U43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="13" t="inlineStr"/>
+      <c r="W43" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:11:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Qwen2.5</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>SFT-PIPPA-other</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>C: best_of=16</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>qwen3b_pippa_r16_bo16</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-pippa-r16_v2</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r16_v2</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen2.5-3B-PIPPA-r16</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="M44" s="15" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="N44" s="13" t="inlineStr"/>
+      <c r="O44" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="S44" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T44" s="13" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="U44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="13" t="inlineStr"/>
+      <c r="W44" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:29:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Qwen2.5</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>SFT-PIPPA-other</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>qwen3b_pippa_r16</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen2.5-3B-PIPPA-r16</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>145</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="M45" s="15" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="N45" s="13" t="inlineStr"/>
+      <c r="O45" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S45" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T45" s="13" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="U45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="13" t="inlineStr"/>
+      <c r="W45" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:29:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Llama-3.2</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>llama32_3b_anime_step30</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_23097_v1</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-step30</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:40:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Llama-3.2</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>llama32_3b_anime_step60</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>zheqiwu-llama-3-2-3b-an_12275_v1</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_12275_v1</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-step60</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:40:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Llama-3.2</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>llama32_3b_anime_step100</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_40296_v1</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-step100</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:40:29</t>
         </is>
       </c>
     </row>
@@ -4396,6 +5051,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4414,7 +5076,7 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -4450,7 +5112,7 @@
       </c>
       <c r="F1" s="16" t="inlineStr">
         <is>
-          <t>Gen variant</t>
+          <t>Gen</t>
         </is>
       </c>
       <c r="G1" s="16" t="inlineStr">
@@ -4509,10 +5171,10 @@
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>5363</v>
+        <v>7314</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>0.3586</v>
+        <v>0.3604</v>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
@@ -4555,10 +5217,10 @@
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>5434</v>
+        <v>7496</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>0.3519</v>
+        <v>0.3522</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
@@ -4601,10 +5263,10 @@
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>5699</v>
+        <v>7719</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>0.3441</v>
+        <v>0.3447</v>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
@@ -4647,10 +5309,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5510</v>
+        <v>7612</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.3274</v>
+        <v>0.3291</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -4693,10 +5355,10 @@
         </is>
       </c>
       <c r="H6" s="18" t="n">
-        <v>5439</v>
+        <v>7497</v>
       </c>
       <c r="I6" s="19" t="n">
-        <v>0.324</v>
+        <v>0.3229</v>
       </c>
       <c r="J6" s="18" t="inlineStr">
         <is>
@@ -4710,12 +5372,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B/C: prompt+gen</t>
+          <t>A: base scan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qwen2.5</t>
+          <t>Llama-3.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4730,23 +5392,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>qwen25_3b_bo16</t>
+          <t>llama32_3b</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5597</v>
+        <v>7854</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>0.3187</v>
+        <v>0.3193</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>qwen-qwen2-5-3b-instruct_v20</t>
+          <t>meta-llama-llama-3-2-3b_30223_v2</t>
         </is>
       </c>
     </row>
@@ -4756,17 +5418,17 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>A: base scan</t>
+          <t>B/C: prompt+gen</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>Llama-3.2</t>
+          <t>Qwen3</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>4B</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -4776,23 +5438,23 @@
       </c>
       <c r="F8" s="18" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
-          <t>llama32_3b</t>
+          <t>qwen3_4b_bo16</t>
         </is>
       </c>
       <c r="H8" s="18" t="n">
-        <v>5853</v>
+        <v>7659</v>
       </c>
       <c r="I8" s="19" t="n">
-        <v>0.3186</v>
+        <v>0.319</v>
       </c>
       <c r="J8" s="18" t="inlineStr">
         <is>
-          <t>meta-llama-llama-3-2-3b_30223_v2</t>
+          <t>qwen-qwen3-4b-instruct-2507_v11</t>
         </is>
       </c>
     </row>
@@ -4807,12 +5469,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qwen3</t>
+          <t>Qwen2.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4827,18 +5489,18 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>qwen3_4b_bo16</t>
+          <t>qwen25_3b_bo16</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5644</v>
+        <v>7602</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.312</v>
+        <v>0.3154</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>qwen-qwen3-4b-instruct-2507_v11</t>
+          <t>qwen-qwen2-5-3b-instruct_v20</t>
         </is>
       </c>
     </row>
@@ -4877,10 +5539,10 @@
         </is>
       </c>
       <c r="H10" s="18" t="n">
-        <v>5653</v>
+        <v>7744</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>0.3059</v>
+        <v>0.3068</v>
       </c>
       <c r="J10" s="18" t="inlineStr">
         <is>
@@ -4923,10 +5585,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5811</v>
+        <v>7852</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>0.2991</v>
+        <v>0.3029</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -4950,7 +5612,7 @@
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>1.7B</t>
+          <t>4B</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -4965,18 +5627,18 @@
       </c>
       <c r="G12" s="18" t="inlineStr">
         <is>
-          <t>qwen3_1p7b</t>
+          <t>qwen3_4b</t>
         </is>
       </c>
       <c r="H12" s="18" t="n">
-        <v>5803</v>
+        <v>7681</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>0.2976</v>
+        <v>0.2966</v>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
-          <t>qwen-qwen3-1-7b_v1</t>
+          <t>qwen-qwen3-4b-instruct-2507_v10</t>
         </is>
       </c>
     </row>
@@ -4996,7 +5658,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>1.7B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5011,18 +5673,18 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>qwen3_4b</t>
+          <t>qwen3_1p7b</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5667</v>
+        <v>7827</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.2936</v>
+        <v>0.2937</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>qwen-qwen3-4b-instruct-2507_v10</t>
+          <t>qwen-qwen3-1-7b_v1</t>
         </is>
       </c>
     </row>
@@ -5061,10 +5723,10 @@
         </is>
       </c>
       <c r="H14" s="18" t="n">
-        <v>5579</v>
+        <v>7559</v>
       </c>
       <c r="I14" s="19" t="n">
-        <v>0.2875</v>
+        <v>0.2914</v>
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
@@ -5107,10 +5769,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5704</v>
+        <v>7686</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.287</v>
+        <v>0.2856</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5153,10 +5815,10 @@
         </is>
       </c>
       <c r="H16" s="18" t="n">
-        <v>5786</v>
+        <v>7787</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>0.2694</v>
+        <v>0.2734</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
@@ -5199,10 +5861,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5789</v>
+        <v>7828</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.2638</v>
+        <v>0.2666</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5245,10 +5907,10 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>5771</v>
+        <v>7804</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>0.2485</v>
+        <v>0.2492</v>
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
@@ -5291,10 +5953,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5748</v>
+        <v>7786</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.1975</v>
+        <v>0.1961</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5314,10 +5976,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -5375,13 +6037,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1380</v>
+        <v>3367</v>
       </c>
       <c r="D2" t="n">
-        <v>397</v>
+        <v>975</v>
       </c>
       <c r="E2" s="17" t="n">
-        <v>0.2877</v>
+        <v>0.2896</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5406,13 +6068,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1397</v>
+        <v>3445</v>
       </c>
       <c r="D3" t="n">
-        <v>380</v>
+        <v>932</v>
       </c>
       <c r="E3" s="17" t="n">
-        <v>0.272</v>
+        <v>0.2705</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5468,13 +6130,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>545</v>
+        <v>2609</v>
       </c>
       <c r="D5" t="n">
-        <v>175</v>
+        <v>781</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>0.3211</v>
+        <v>0.2993</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -5495,26 +6157,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200</t>
+          <t>qwen3b_coser_step200_coser_guide</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>584</v>
+        <v>2683</v>
       </c>
       <c r="D6" t="n">
-        <v>159</v>
+        <v>723</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>0.2723</v>
+        <v>0.2695</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v1</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>B: +CoSER guide</t>
         </is>
       </c>
     </row>
@@ -5526,26 +6188,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200_coser_guide</t>
+          <t>qwen3b_coser_step200</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>571</v>
+        <v>2571</v>
       </c>
       <c r="D7" t="n">
-        <v>151</v>
+        <v>670</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>0.2644</v>
+        <v>0.2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v3</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B: +CoSER guide</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -5561,13 +6223,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>303</v>
+        <v>2457</v>
       </c>
       <c r="D8" t="n">
-        <v>83</v>
+        <v>709</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.2739</v>
+        <v>0.2886</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -5592,13 +6254,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>285</v>
+        <v>2399</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>666</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>0.2561</v>
+        <v>0.2776</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -5623,13 +6285,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>305</v>
+        <v>2327</v>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>572</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>0.2426</v>
+        <v>0.2458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -5639,401 +6301,223 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>B: +CoSER guide</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B1" s="20" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C1" s="20" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Counts</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Total submissions</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Counts</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>≥5000 battles</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Counts</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Currently deployed</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Counts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Torndown / dead</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Counts</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0 battles (failed deploy)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Top (≥5k battles)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>#1 win_ratio</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>35.86% (qwen3_30b_a3b_bo16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Top (≥5k battles)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>#1 submission_id</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>qwen-qwen3-30b-a3b-inst_16638_v4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Top (≥5k battles)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>#2 win_ratio</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>35.19% (qwen3_4b_long)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Top (≥5k battles)</t>
+          <t>SFT-PIPPA-r32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#3 win_ratio</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>34.41% (qwen3_30b_a3b)</t>
+          <t>qwen3b_pippa_r32_bo16</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>793</v>
+      </c>
+      <c r="D11" t="n">
+        <v>242</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SFT-PIPPA-r32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>qwen3b_pippa_r32</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>773</v>
+      </c>
+      <c r="D12" t="n">
+        <v>213</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Avg win_ratio (≥5k)</t>
+          <t>SFT-PIPPA-other</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A: base scan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>28.14% (n=9)</t>
+          <t>qwen3b_pippa_r16_bo16</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>120</v>
+      </c>
+      <c r="D13" t="n">
+        <v>39</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-pippa-r16_v2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Avg win_ratio (≥5k)</t>
+          <t>SFT-PIPPA-other</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B/C: prompt+gen</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>31.92% (n=9)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Color/value</t>
-        </is>
-      </c>
-      <c r="B1" s="20" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Blue band</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Dim A — base model scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Green band</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Dim B/C — prompt+gen sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Yellow band</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Dim D — SFT-fine-tuned model</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bright green row</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Top-3 by win_ratio (among ≥5000 battles)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Red band</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0 battles — failed deploy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>≥5k? column</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>✓ if ≥5000 battles, else blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Submitted under current Chai rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>active_max80</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Resubmit at max_output_tokens=80</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>completed_old_max128</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>First-fire ran with max_out=128 before validation tightened</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
+          <t>qwen3b_pippa_r16</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>145</v>
+      </c>
+      <c r="D14" t="n">
+        <v>47</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>SFT-other</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>All elo=9999 entries are pre-Elo-calibration; Chai assigns 9999 as a placeholder until Elo finalizes</t>
+          <t>llama32_3b_anime_step30</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>llama32_3b_anime_step60</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>zheqiwu-llama-3-2-3b-an_12275_v1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>llama32_3b_anime_step100</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>default</t>
         </is>
       </c>
     </row>

--- a/Onsite/submissions.xlsx
+++ b/Onsite/submissions.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W71"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3860,13 +3860,13 @@
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>3185</v>
+        <v>3698</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>902</v>
+        <v>1054</v>
       </c>
       <c r="M36" s="15" t="n">
-        <v>0.2832</v>
+        <v>0.285</v>
       </c>
       <c r="N36" s="13" t="inlineStr"/>
       <c r="O36" s="13" t="inlineStr">
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>2300</v>
+        <v>2796</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>637</v>
+        <v>750</v>
       </c>
       <c r="M37" s="15" t="n">
-        <v>0.277</v>
+        <v>0.2682</v>
       </c>
       <c r="N37" s="13" t="inlineStr"/>
       <c r="O37" s="13" t="inlineStr">
@@ -4029,41 +4029,37 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200_bo16</t>
+          <t>qwen3b_synth_step200_bo16</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v2</t>
+          <t>zheqiwu-qwen2-5-3b-synt_99089_v1</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_99089_v1</t>
         </is>
       </c>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen2.5-3B-CoSER-step200</t>
+          <t>ZheqiWu/Qwen2.5-3B-synth-step200</t>
         </is>
       </c>
       <c r="K38" s="13" t="n">
-        <v>10220</v>
+        <v>325</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>3034</v>
+        <v>97</v>
       </c>
       <c r="M38" s="15" t="n">
-        <v>0.2969</v>
-      </c>
-      <c r="N38" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2985</v>
+      </c>
+      <c r="N38" s="13" t="inlineStr"/>
       <c r="O38" s="13" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>deployed</t>
         </is>
       </c>
       <c r="P38" s="13" t="n">
@@ -4090,7 +4086,7 @@
       <c r="V38" s="13" t="inlineStr"/>
       <c r="W38" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T21:17:02</t>
+          <t>2026-06-20T04:25:28</t>
         </is>
       </c>
     </row>
@@ -4122,22 +4118,22 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>B: +CoSER guide</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200_coser_guide</t>
+          <t>qwen3b_coser_step200_bo16</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v3</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v2</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v3</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v2</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
@@ -4146,13 +4142,13 @@
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>10150</v>
+        <v>10220</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>2798</v>
+        <v>3034</v>
       </c>
       <c r="M39" s="15" t="n">
-        <v>0.2757</v>
+        <v>0.2969</v>
       </c>
       <c r="N39" s="13" t="inlineStr">
         <is>
@@ -4171,7 +4167,7 @@
         <v>1</v>
       </c>
       <c r="R39" s="13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S39" s="13" t="n">
         <v>64</v>
@@ -4188,7 +4184,7 @@
       <c r="V39" s="13" t="inlineStr"/>
       <c r="W39" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T21:17:04</t>
+          <t>2026-06-19T21:17:02</t>
         </is>
       </c>
     </row>
@@ -4220,22 +4216,22 @@
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>B: +CoSER guide</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200</t>
+          <t>qwen3b_coser_step200_coser_guide</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v1</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v3</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v3</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr">
@@ -4244,13 +4240,13 @@
         </is>
       </c>
       <c r="K40" s="13" t="n">
-        <v>10194</v>
+        <v>10150</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>2690</v>
+        <v>2798</v>
       </c>
       <c r="M40" s="15" t="n">
-        <v>0.2639</v>
+        <v>0.2757</v>
       </c>
       <c r="N40" s="13" t="inlineStr">
         <is>
@@ -4286,7 +4282,7 @@
       <c r="V40" s="13" t="inlineStr"/>
       <c r="W40" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T21:17:00</t>
+          <t>2026-06-19T21:17:04</t>
         </is>
       </c>
     </row>
@@ -4313,42 +4309,42 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>SFT-step500</t>
+          <t>SFT-step200</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step500_bo16</t>
+          <t>qwen3b_coser_step200</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_40142_v2</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v1</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_40142_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v1</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen2.5-3B-CoSER-step500</t>
+          <t>ZheqiWu/Qwen2.5-3B-CoSER-step200</t>
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>10374</v>
+        <v>10194</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>3009</v>
+        <v>2690</v>
       </c>
       <c r="M41" s="15" t="n">
-        <v>0.2901</v>
+        <v>0.2639</v>
       </c>
       <c r="N41" s="13" t="inlineStr">
         <is>
@@ -4367,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="R41" s="13" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S41" s="13" t="n">
         <v>64</v>
@@ -4384,7 +4380,7 @@
       <c r="V41" s="13" t="inlineStr"/>
       <c r="W41" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T21:24:34</t>
+          <t>2026-06-19T21:17:00</t>
         </is>
       </c>
     </row>
@@ -4416,22 +4412,22 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step500</t>
+          <t>qwen3b_coser_step500_bo16</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_40142_v1</t>
+          <t>zheqiwu-qwen2-5-3b-cose_40142_v2</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_40142_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_40142_v2</t>
         </is>
       </c>
       <c r="J42" s="13" t="inlineStr">
@@ -4440,13 +4436,13 @@
         </is>
       </c>
       <c r="K42" s="13" t="n">
-        <v>10286</v>
+        <v>10374</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>2721</v>
+        <v>3009</v>
       </c>
       <c r="M42" s="15" t="n">
-        <v>0.2645</v>
+        <v>0.2901</v>
       </c>
       <c r="N42" s="13" t="inlineStr">
         <is>
@@ -4465,7 +4461,7 @@
         <v>1</v>
       </c>
       <c r="R42" s="13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S42" s="13" t="n">
         <v>64</v>
@@ -4482,7 +4478,7 @@
       <c r="V42" s="13" t="inlineStr"/>
       <c r="W42" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T21:24:32</t>
+          <t>2026-06-19T21:24:34</t>
         </is>
       </c>
     </row>
@@ -4514,22 +4510,22 @@
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>B: +CoSER guide</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step500_coser_guide</t>
+          <t>qwen3b_coser_step500</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_40142_v3</t>
+          <t>zheqiwu-qwen2-5-3b-cose_40142_v1</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_40142_v3</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_40142_v1</t>
         </is>
       </c>
       <c r="J43" s="13" t="inlineStr">
@@ -4538,13 +4534,13 @@
         </is>
       </c>
       <c r="K43" s="13" t="n">
-        <v>10142</v>
+        <v>10286</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>2616</v>
+        <v>2721</v>
       </c>
       <c r="M43" s="15" t="n">
-        <v>0.2579</v>
+        <v>0.2645</v>
       </c>
       <c r="N43" s="13" t="inlineStr">
         <is>
@@ -4580,7 +4576,7 @@
       <c r="V43" s="13" t="inlineStr"/>
       <c r="W43" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T21:24:35</t>
+          <t>2026-06-19T21:24:32</t>
         </is>
       </c>
     </row>
@@ -4607,42 +4603,42 @@
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>SFT-PIPPA-r32</t>
+          <t>SFT-step500</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>B: +CoSER guide</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r32_bo16</t>
+          <t>qwen3b_coser_step500_coser_guide</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
+          <t>zheqiwu-qwen2-5-3b-cose_40142_v3</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_40142_v3</t>
         </is>
       </c>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen2.5-3B-PIPPA-r32</t>
+          <t>ZheqiWu/Qwen2.5-3B-CoSER-step500</t>
         </is>
       </c>
       <c r="K44" s="13" t="n">
-        <v>8853</v>
+        <v>10142</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>2664</v>
+        <v>2616</v>
       </c>
       <c r="M44" s="15" t="n">
-        <v>0.3009</v>
+        <v>0.2579</v>
       </c>
       <c r="N44" s="13" t="inlineStr">
         <is>
@@ -4651,7 +4647,7 @@
       </c>
       <c r="O44" s="13" t="inlineStr">
         <is>
-          <t>deployed</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="P44" s="13" t="n">
@@ -4661,7 +4657,7 @@
         <v>1</v>
       </c>
       <c r="R44" s="13" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S44" s="13" t="n">
         <v>64</v>
@@ -4678,7 +4674,7 @@
       <c r="V44" s="13" t="inlineStr"/>
       <c r="W44" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T22:11:31</t>
+          <t>2026-06-19T21:24:35</t>
         </is>
       </c>
     </row>
@@ -4710,22 +4706,22 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r32</t>
+          <t>qwen3b_pippa_r32_bo16</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
         </is>
       </c>
       <c r="J45" s="13" t="inlineStr">
@@ -4734,13 +4730,13 @@
         </is>
       </c>
       <c r="K45" s="13" t="n">
-        <v>8675</v>
+        <v>9341</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>2499</v>
+        <v>2808</v>
       </c>
       <c r="M45" s="15" t="n">
-        <v>0.2881</v>
+        <v>0.3006</v>
       </c>
       <c r="N45" s="13" t="inlineStr">
         <is>
@@ -4759,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="R45" s="13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S45" s="13" t="n">
         <v>64</v>
@@ -4776,7 +4772,7 @@
       <c r="V45" s="13" t="inlineStr"/>
       <c r="W45" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T22:11:29</t>
+          <t>2026-06-19T22:11:31</t>
         </is>
       </c>
     </row>
@@ -4803,42 +4799,42 @@
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>SFT-PIPPA-other</t>
+          <t>SFT-PIPPA-r32</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r16_bo16</t>
+          <t>qwen3b_pippa_r32</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r16_v2</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r16_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
         </is>
       </c>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen2.5-3B-PIPPA-r16</t>
+          <t>ZheqiWu/Qwen2.5-3B-PIPPA-r32</t>
         </is>
       </c>
       <c r="K46" s="13" t="n">
-        <v>8092</v>
+        <v>9203</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>2454</v>
+        <v>2654</v>
       </c>
       <c r="M46" s="15" t="n">
-        <v>0.3033</v>
+        <v>0.2884</v>
       </c>
       <c r="N46" s="13" t="inlineStr">
         <is>
@@ -4857,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="R46" s="13" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S46" s="13" t="n">
         <v>64</v>
@@ -4874,7 +4870,7 @@
       <c r="V46" s="13" t="inlineStr"/>
       <c r="W46" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T22:29:33</t>
+          <t>2026-06-19T22:11:29</t>
         </is>
       </c>
     </row>
@@ -4906,22 +4902,22 @@
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r16</t>
+          <t>qwen3b_pippa_r16_bo16</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r16_v2</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r16_v2</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -4930,13 +4926,13 @@
         </is>
       </c>
       <c r="K47" s="13" t="n">
-        <v>8104</v>
+        <v>8620</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>2345</v>
+        <v>2616</v>
       </c>
       <c r="M47" s="15" t="n">
-        <v>0.2894</v>
+        <v>0.3035</v>
       </c>
       <c r="N47" s="13" t="inlineStr">
         <is>
@@ -4955,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="R47" s="13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S47" s="13" t="n">
         <v>64</v>
@@ -4972,7 +4968,7 @@
       <c r="V47" s="13" t="inlineStr"/>
       <c r="W47" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T22:29:31</t>
+          <t>2026-06-19T22:29:33</t>
         </is>
       </c>
     </row>
@@ -4989,7 +4985,7 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>Llama-3.2</t>
+          <t>Qwen2.5</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
@@ -4999,7 +4995,7 @@
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>SFT-other</t>
+          <t>SFT-PIPPA-other</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -5009,34 +5005,38 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v2_step100</t>
+          <t>qwen3b_pippa_r16</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_94942_v1</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_94942_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
         </is>
       </c>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Llama-3.2-3B-Anime-v2-step100</t>
+          <t>ZheqiWu/Qwen2.5-3B-PIPPA-r16</t>
         </is>
       </c>
       <c r="K48" s="13" t="n">
-        <v>3121</v>
+        <v>8675</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>938</v>
+        <v>2509</v>
       </c>
       <c r="M48" s="15" t="n">
-        <v>0.3005</v>
-      </c>
-      <c r="N48" s="13" t="inlineStr"/>
+        <v>0.2892</v>
+      </c>
+      <c r="N48" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O48" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -5066,7 +5066,7 @@
       <c r="V48" s="13" t="inlineStr"/>
       <c r="W48" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T01:28:29</t>
+          <t>2026-06-19T22:29:31</t>
         </is>
       </c>
     </row>
@@ -5103,38 +5103,34 @@
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step100</t>
+          <t>llama32_3b_anime_v2_step300</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_65099_v1</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_40296_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_65099_v1</t>
         </is>
       </c>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Llama-3.2-3B-Anime-step100</t>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-v2-step300</t>
         </is>
       </c>
       <c r="K49" s="13" t="n">
-        <v>7584</v>
+        <v>3682</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>2278</v>
+        <v>1113</v>
       </c>
       <c r="M49" s="15" t="n">
-        <v>0.3004</v>
-      </c>
-      <c r="N49" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.3023</v>
+      </c>
+      <c r="N49" s="13" t="inlineStr"/>
       <c r="O49" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -5164,7 +5160,7 @@
       <c r="V49" s="13" t="inlineStr"/>
       <c r="W49" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T22:40:29</t>
+          <t>2026-06-20T01:28:32</t>
         </is>
       </c>
     </row>
@@ -5201,34 +5197,38 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v2_step300</t>
+          <t>llama32_3b_anime_step100</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_65099_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_65099_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_40296_v1</t>
         </is>
       </c>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Llama-3.2-3B-Anime-v2-step300</t>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-step100</t>
         </is>
       </c>
       <c r="K50" s="13" t="n">
-        <v>3149</v>
+        <v>8085</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>942</v>
+        <v>2432</v>
       </c>
       <c r="M50" s="15" t="n">
-        <v>0.2991</v>
-      </c>
-      <c r="N50" s="13" t="inlineStr"/>
+        <v>0.3008</v>
+      </c>
+      <c r="N50" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O50" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -5258,7 +5258,7 @@
       <c r="V50" s="13" t="inlineStr"/>
       <c r="W50" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T01:28:32</t>
+          <t>2026-06-19T22:40:29</t>
         </is>
       </c>
     </row>
@@ -5295,32 +5295,32 @@
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v3_gpt_step100</t>
+          <t>llama32_3b_anime_v2_step100</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_93952_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_94942_v1</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_93952_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_94942_v1</t>
         </is>
       </c>
       <c r="J51" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Llama-3.2-3B-Anime-v3-gpt-step100</t>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-v2-step100</t>
         </is>
       </c>
       <c r="K51" s="13" t="n">
-        <v>2202</v>
+        <v>3667</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>643</v>
+        <v>1086</v>
       </c>
       <c r="M51" s="15" t="n">
-        <v>0.292</v>
+        <v>0.2962</v>
       </c>
       <c r="N51" s="13" t="inlineStr"/>
       <c r="O51" s="13" t="inlineStr">
@@ -5352,7 +5352,7 @@
       <c r="V51" s="13" t="inlineStr"/>
       <c r="W51" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T02:14:03</t>
+          <t>2026-06-20T01:28:29</t>
         </is>
       </c>
     </row>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="K52" s="13" t="n">
-        <v>7619</v>
+        <v>8203</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>2220</v>
+        <v>2390</v>
       </c>
       <c r="M52" s="15" t="n">
         <v>0.2914</v>
@@ -5487,38 +5487,34 @@
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step30</t>
+          <t>llama32_3b_anime_v3_gpt_step100</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_93952_v1</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_23097_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_93952_v1</t>
         </is>
       </c>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Llama-3.2-3B-Anime-step30</t>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-v3-gpt-step100</t>
         </is>
       </c>
       <c r="K53" s="13" t="n">
-        <v>7708</v>
+        <v>2754</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>2206</v>
+        <v>793</v>
       </c>
       <c r="M53" s="15" t="n">
-        <v>0.2862</v>
-      </c>
-      <c r="N53" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2879</v>
+      </c>
+      <c r="N53" s="13" t="inlineStr"/>
       <c r="O53" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -5548,7 +5544,7 @@
       <c r="V53" s="13" t="inlineStr"/>
       <c r="W53" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T22:40:26</t>
+          <t>2026-06-20T02:14:03</t>
         </is>
       </c>
     </row>
@@ -5604,13 +5600,13 @@
         </is>
       </c>
       <c r="K54" s="13" t="n">
-        <v>2165</v>
+        <v>2658</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>617</v>
+        <v>764</v>
       </c>
       <c r="M54" s="15" t="n">
-        <v>0.285</v>
+        <v>0.2874</v>
       </c>
       <c r="N54" s="13" t="inlineStr"/>
       <c r="O54" s="13" t="inlineStr">
@@ -5659,7 +5655,7 @@
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>Qwen3</t>
+          <t>Llama-3.2</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
@@ -5679,34 +5675,38 @@
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo64</t>
+          <t>llama32_3b_anime_step30</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v5</t>
+          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v5</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_23097_v1</t>
         </is>
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-step30</t>
         </is>
       </c>
       <c r="K55" s="13" t="n">
-        <v>1450</v>
+        <v>8246</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>532</v>
+        <v>2349</v>
       </c>
       <c r="M55" s="15" t="n">
-        <v>0.3669</v>
-      </c>
-      <c r="N55" s="13" t="inlineStr"/>
+        <v>0.2849</v>
+      </c>
+      <c r="N55" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O55" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -5719,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="R55" s="13" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="S55" s="13" t="n">
         <v>64</v>
@@ -5736,7 +5736,7 @@
       <c r="V55" s="13" t="inlineStr"/>
       <c r="W55" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T02:58:34</t>
+          <t>2026-06-19T22:40:26</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>Qwen3</t>
+          <t>Qwen2.5</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
@@ -5768,37 +5768,37 @@
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>C: long-out (max=80)</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step100_long</t>
+          <t>qwen3b_synth_step100_bo16</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-s_1701_v2</t>
+          <t>zheqiwu-qwen2-5-3b-synt_62780_v1</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_1701_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_62780_v1</t>
         </is>
       </c>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step100</t>
+          <t>ZheqiWu/Qwen2.5-3B-synth-step100</t>
         </is>
       </c>
       <c r="K56" s="13" t="n">
-        <v>1448</v>
+        <v>339</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>522</v>
+        <v>97</v>
       </c>
       <c r="M56" s="15" t="n">
-        <v>0.3605</v>
+        <v>0.2861</v>
       </c>
       <c r="N56" s="13" t="inlineStr"/>
       <c r="O56" s="13" t="inlineStr">
@@ -5813,14 +5813,15 @@
         <v>1</v>
       </c>
       <c r="R56" s="13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S56" s="13" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="T56" s="13" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>
+</t>
         </is>
       </c>
       <c r="U56" s="13" t="n">
@@ -5829,7 +5830,7 @@
       <c r="V56" s="13" t="inlineStr"/>
       <c r="W56" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T02:56:43</t>
+          <t>2026-06-20T04:25:26</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5847,7 @@
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>Qwen3</t>
+          <t>Qwen2.5</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
@@ -5861,37 +5862,37 @@
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>C: long-out (max=80)</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_long</t>
+          <t>qwen3b_synth_step60_bo16</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v3</t>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v2</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v3</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_19065_v2</t>
         </is>
       </c>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+          <t>ZheqiWu/Qwen2.5-3B-synth-step60</t>
         </is>
       </c>
       <c r="K57" s="13" t="n">
-        <v>1466</v>
+        <v>319</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>524</v>
+        <v>83</v>
       </c>
       <c r="M57" s="15" t="n">
-        <v>0.3574</v>
+        <v>0.2602</v>
       </c>
       <c r="N57" s="13" t="inlineStr"/>
       <c r="O57" s="13" t="inlineStr">
@@ -5906,14 +5907,15 @@
         <v>1</v>
       </c>
       <c r="R57" s="13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S57" s="13" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="T57" s="13" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>
+</t>
         </is>
       </c>
       <c r="U57" s="13" t="n">
@@ -5922,7 +5924,7 @@
       <c r="V57" s="13" t="inlineStr"/>
       <c r="W57" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T02:56:42</t>
+          <t>2026-06-20T04:25:23</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5941,7 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>Qwen3</t>
+          <t>Qwen2.5</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
@@ -5959,32 +5961,32 @@
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step30_bo32</t>
+          <t>qwen3b_synth_step60</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v4</t>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v1</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v4</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_19065_v1</t>
         </is>
       </c>
       <c r="J58" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
+          <t>ZheqiWu/Qwen2.5-3B-synth-step60</t>
         </is>
       </c>
       <c r="K58" s="13" t="n">
-        <v>1479</v>
+        <v>328</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>499</v>
+        <v>85</v>
       </c>
       <c r="M58" s="15" t="n">
-        <v>0.3374</v>
+        <v>0.2591</v>
       </c>
       <c r="N58" s="13" t="inlineStr"/>
       <c r="O58" s="13" t="inlineStr">
@@ -5999,7 +6001,7 @@
         <v>1</v>
       </c>
       <c r="R58" s="13" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="S58" s="13" t="n">
         <v>64</v>
@@ -6016,7 +6018,7 @@
       <c r="V58" s="13" t="inlineStr"/>
       <c r="W58" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T02:58:36</t>
+          <t>2026-06-20T04:25:22</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6035,7 @@
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>Qwen3</t>
+          <t>Qwen2.5</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
@@ -6048,43 +6050,39 @@
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo16</t>
+          <t>qwen3b_synth_step60_bo32</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v2</t>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v3</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_19065_v3</t>
         </is>
       </c>
       <c r="J59" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+          <t>ZheqiWu/Qwen2.5-3B-synth-step60</t>
         </is>
       </c>
       <c r="K59" s="13" t="n">
-        <v>7288</v>
+        <v>301</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2453</v>
+        <v>74</v>
       </c>
       <c r="M59" s="15" t="n">
-        <v>0.3366</v>
-      </c>
-      <c r="N59" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2458</v>
+      </c>
+      <c r="N59" s="13" t="inlineStr"/>
       <c r="O59" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -6097,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="R59" s="13" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="S59" s="13" t="n">
         <v>64</v>
@@ -6114,7 +6112,7 @@
       <c r="V59" s="13" t="inlineStr"/>
       <c r="W59" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T22:59:04</t>
+          <t>2026-06-20T04:25:25</t>
         </is>
       </c>
     </row>
@@ -6146,43 +6144,39 @@
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>C: long-out (max=80)</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step30_bo16</t>
+          <t>qwen3_4b_anime_step100_bo64_long</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v2</t>
+          <t>zheqiwu-qwen3-4b-anime-s_1701_v3</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_1701_v3</t>
         </is>
       </c>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
+          <t>ZheqiWu/Qwen3-4B-Anime-step100</t>
         </is>
       </c>
       <c r="K60" s="13" t="n">
-        <v>7148</v>
+        <v>381</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>2357</v>
+        <v>150</v>
       </c>
       <c r="M60" s="15" t="n">
-        <v>0.3297</v>
-      </c>
-      <c r="N60" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.3937</v>
+      </c>
+      <c r="N60" s="13" t="inlineStr"/>
       <c r="O60" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -6195,1066 +6189,1542 @@
         <v>1</v>
       </c>
       <c r="R60" s="13" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="S60" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="T60" s="13" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="U60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="13" t="inlineStr"/>
+      <c r="W60" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:21:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step60_bo128</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step60_v8</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v8</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="n">
+        <v>376</v>
+      </c>
+      <c r="L61" s="13" t="n">
+        <v>141</v>
+      </c>
+      <c r="M61" s="15" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N61" s="13" t="inlineStr"/>
+      <c r="O61" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="S61" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="T60" s="13" t="inlineStr">
+      <c r="T61" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U60" s="13" t="n">
+      <c r="U61" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="13" t="inlineStr"/>
-      <c r="W60" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-19T22:59:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="V61" s="13" t="inlineStr"/>
+      <c r="W61" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:21:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>D: SFT</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>SFT-other</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="F62" s="13" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step100</t>
-        </is>
-      </c>
-      <c r="H61" s="13" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-s_1701_v1</t>
-        </is>
-      </c>
-      <c r="I61" s="14" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_1701_v1</t>
-        </is>
-      </c>
-      <c r="J61" s="13" t="inlineStr">
-        <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step100</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="n">
-        <v>7048</v>
-      </c>
-      <c r="L61" s="13" t="n">
-        <v>2259</v>
-      </c>
-      <c r="M61" s="15" t="n">
-        <v>0.3205</v>
-      </c>
-      <c r="N61" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O61" s="13" t="inlineStr">
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step60_bo64</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step60_v5</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v5</t>
+        </is>
+      </c>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>2008</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>725</v>
+      </c>
+      <c r="M62" s="15" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="N62" s="13" t="inlineStr"/>
+      <c r="O62" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
         </is>
       </c>
-      <c r="P61" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="S61" s="13" t="n">
+      <c r="P62" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="T61" s="13" t="inlineStr">
+      <c r="S62" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T62" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U61" s="13" t="n">
+      <c r="U62" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="13" t="inlineStr"/>
-      <c r="W61" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-19T22:59:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="13" t="inlineStr">
+      <c r="V62" s="13" t="inlineStr"/>
+      <c r="W62" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:58:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>D: SFT</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C62" s="13" t="inlineStr">
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>SFT-other</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step60_bo32</t>
-        </is>
-      </c>
-      <c r="H62" s="13" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v4</t>
-        </is>
-      </c>
-      <c r="I62" s="14" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v4</t>
-        </is>
-      </c>
-      <c r="J62" s="13" t="inlineStr">
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>C: long-out (max=80)</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step100_long</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-s_1701_v2</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_1701_v2</t>
+        </is>
+      </c>
+      <c r="J63" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step100</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>1996</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>717</v>
+      </c>
+      <c r="M63" s="15" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="N63" s="13" t="inlineStr"/>
+      <c r="O63" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P63" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S63" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="T63" s="13" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="U63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="13" t="inlineStr"/>
+      <c r="W63" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:56:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>C: long-out (max=80)</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step60_long_freqpen</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step60_v9</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v9</t>
+        </is>
+      </c>
+      <c r="J64" s="13" t="inlineStr">
         <is>
           <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
         </is>
       </c>
-      <c r="K62" s="13" t="n">
-        <v>1394</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>436</v>
-      </c>
-      <c r="M62" s="15" t="n">
-        <v>0.3128</v>
-      </c>
-      <c r="N62" s="13" t="inlineStr"/>
-      <c r="O62" s="13" t="inlineStr">
+      <c r="K64" s="13" t="n">
+        <v>376</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>131</v>
+      </c>
+      <c r="M64" s="15" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="N64" s="13" t="inlineStr"/>
+      <c r="O64" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
         </is>
       </c>
-      <c r="P62" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q62" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="S62" s="13" t="n">
+      <c r="P64" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S64" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="T64" s="13" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="U64" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V64" s="13" t="inlineStr"/>
+      <c r="W64" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:21:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>C: long-out (max=80)</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step60_long</t>
+        </is>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step60_v3</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v3</t>
+        </is>
+      </c>
+      <c r="J65" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>2010</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>695</v>
+      </c>
+      <c r="M65" s="15" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="N65" s="13" t="inlineStr"/>
+      <c r="O65" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S65" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="T65" s="13" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="U65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="13" t="inlineStr"/>
+      <c r="W65" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:56:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="inlineStr">
+        <is>
+          <t>C: best_of=16</t>
+        </is>
+      </c>
+      <c r="G66" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step60_bo16</t>
+        </is>
+      </c>
+      <c r="H66" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step60_v2</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v2</t>
+        </is>
+      </c>
+      <c r="J66" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>7845</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>2647</v>
+      </c>
+      <c r="M66" s="15" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="N66" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O66" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P66" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="S66" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="T62" s="13" t="inlineStr">
+      <c r="T66" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U62" s="13" t="n">
+      <c r="U66" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="13" t="inlineStr"/>
-      <c r="W62" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-20T02:58:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="V66" s="13" t="inlineStr"/>
+      <c r="W66" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:59:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>D: SFT</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>SFT-other</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step60</t>
-        </is>
-      </c>
-      <c r="H63" s="13" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v1</t>
-        </is>
-      </c>
-      <c r="I63" s="14" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v1</t>
-        </is>
-      </c>
-      <c r="J63" s="13" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>C: conservative (T=0.8)</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step60_bo64_tight</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-s_453_v10</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_453_v10</t>
+        </is>
+      </c>
+      <c r="J67" s="13" t="inlineStr">
         <is>
           <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
         </is>
       </c>
-      <c r="K63" s="13" t="n">
-        <v>7092</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>2203</v>
-      </c>
-      <c r="M63" s="15" t="n">
-        <v>0.3106</v>
-      </c>
-      <c r="N63" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O63" s="13" t="inlineStr">
+      <c r="K67" s="13" t="n">
+        <v>386</v>
+      </c>
+      <c r="L67" s="13" t="n">
+        <v>129</v>
+      </c>
+      <c r="M67" s="15" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="N67" s="13" t="inlineStr"/>
+      <c r="O67" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
         </is>
       </c>
-      <c r="P63" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R63" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="S63" s="13" t="n">
+      <c r="P67" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q67" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R67" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="T63" s="13" t="inlineStr">
+      <c r="S67" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T67" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U63" s="13" t="n">
+      <c r="U67" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="13" t="inlineStr"/>
-      <c r="W63" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-19T22:59:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="V67" s="13" t="inlineStr"/>
+      <c r="W67" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:21:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>D: SFT</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t>SFT-other</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
-        <is>
-          <t>C: long-out (max=80)</t>
-        </is>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step30_long</t>
-        </is>
-      </c>
-      <c r="H64" s="13" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v3</t>
-        </is>
-      </c>
-      <c r="I64" s="14" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v3</t>
-        </is>
-      </c>
-      <c r="J64" s="13" t="inlineStr">
-        <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
-        </is>
-      </c>
-      <c r="K64" s="13" t="n">
-        <v>1524</v>
-      </c>
-      <c r="L64" s="13" t="n">
-        <v>469</v>
-      </c>
-      <c r="M64" s="15" t="n">
-        <v>0.3077</v>
-      </c>
-      <c r="N64" s="13" t="inlineStr"/>
-      <c r="O64" s="13" t="inlineStr">
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step60_bo64_v2</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step60_v7</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v7</t>
+        </is>
+      </c>
+      <c r="J68" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>425</v>
+      </c>
+      <c r="L68" s="13" t="n">
+        <v>142</v>
+      </c>
+      <c r="M68" s="15" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="N68" s="13" t="inlineStr"/>
+      <c r="O68" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
         </is>
       </c>
-      <c r="P64" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q64" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="S64" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="T64" s="13" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="U64" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="13" t="inlineStr"/>
-      <c r="W64" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-20T02:56:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>D: SFT</t>
-        </is>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C65" s="13" t="inlineStr">
-        <is>
-          <t>Qwen3</t>
-        </is>
-      </c>
-      <c r="D65" s="13" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>SFT-other</t>
-        </is>
-      </c>
-      <c r="F65" s="13" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G65" s="13" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step30</t>
-        </is>
-      </c>
-      <c r="H65" s="13" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v1</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v1</t>
-        </is>
-      </c>
-      <c r="J65" s="13" t="inlineStr">
-        <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
-        </is>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>7266</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>2175</v>
-      </c>
-      <c r="M65" s="15" t="n">
-        <v>0.2993</v>
-      </c>
-      <c r="N65" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O65" s="13" t="inlineStr">
-        <is>
-          <t>deployed</t>
-        </is>
-      </c>
-      <c r="P65" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R65" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="S65" s="13" t="n">
+      <c r="P68" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="T65" s="13" t="inlineStr">
+      <c r="S68" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T68" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U65" s="13" t="n">
+      <c r="U68" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="13" t="inlineStr"/>
-      <c r="W65" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-19T22:59:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="V68" s="13" t="inlineStr"/>
+      <c r="W68" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:21:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>D: SFT</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C69" s="13" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>SFT-other</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>C: conservative (T=0.8)</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step60_bo64_tight</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-s_453_v10</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_453_v10</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q66" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="R66" s="2" t="n">
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>C: best_of=16</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step30_bo16</t>
+        </is>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step30_v2</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v2</t>
+        </is>
+      </c>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>7725</v>
+      </c>
+      <c r="L69" s="13" t="n">
+        <v>2556</v>
+      </c>
+      <c r="M69" s="15" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="N69" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O69" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P69" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="S69" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="S66" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="T66" s="2" t="inlineStr">
+      <c r="T69" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U66" s="2" t="n">
+      <c r="U69" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="2" t="inlineStr"/>
-      <c r="W66" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-20T04:21:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="V69" s="13" t="inlineStr"/>
+      <c r="W69" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:59:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t>D: SFT</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
         <is>
           <t>SFT-other</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F70" s="13" t="inlineStr">
         <is>
           <t>C: long-out (max=80)</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>qwen3_4b_anime_step60_bo64_long</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H70" s="13" t="inlineStr">
         <is>
           <t>zheqiwu-qwen3-4b-anime-step60_v6</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="I70" s="14" t="inlineStr">
         <is>
           <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v6</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J70" s="13" t="inlineStr">
         <is>
           <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
         </is>
       </c>
-      <c r="K67" s="2" t="n">
+      <c r="K70" s="13" t="n">
+        <v>393</v>
+      </c>
+      <c r="L70" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="M70" s="15" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="N70" s="13" t="inlineStr"/>
+      <c r="O70" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P70" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="S70" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="T70" s="13" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="U70" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R67" s="2" t="n">
+      <c r="V70" s="13" t="inlineStr"/>
+      <c r="W70" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:21:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step30_bo32</t>
+        </is>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step30_v4</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v4</t>
+        </is>
+      </c>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L71" s="13" t="n">
+        <v>663</v>
+      </c>
+      <c r="M71" s="15" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="N71" s="13" t="inlineStr"/>
+      <c r="O71" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P71" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="S71" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="S67" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="T67" s="2" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="U67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" s="2" t="inlineStr"/>
-      <c r="W67" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-20T04:21:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>D: SFT</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Qwen3</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>SFT-other</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>C: long-out (max=80)</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step100_bo64_long</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-s_1701_v3</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_1701_v3</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step100</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R68" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="S68" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="T68" s="2" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="U68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" s="2" t="inlineStr"/>
-      <c r="W68" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-20T04:21:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>D: SFT</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Qwen3</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>SFT-other</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>C: long-out (max=80)</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step60_long_freqpen</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v9</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v9</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S69" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="T69" s="2" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="U69" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="V69" s="2" t="inlineStr"/>
-      <c r="W69" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-20T04:21:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>D: SFT</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Qwen3</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>SFT-other</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step60_bo64_v2</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v7</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v7</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="S70" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="T70" s="2" t="inlineStr">
+      <c r="T71" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U70" s="2" t="n">
+      <c r="U71" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="2" t="inlineStr"/>
-      <c r="W70" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-20T04:21:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="V71" s="13" t="inlineStr"/>
+      <c r="W71" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:58:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>D: SFT</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="13" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="13" t="inlineStr">
         <is>
           <t>SFT-other</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="13" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step60_bo128</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v8</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v8</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step60_bo32</t>
+        </is>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step60_v4</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v4</t>
+        </is>
+      </c>
+      <c r="J72" s="13" t="inlineStr">
         <is>
           <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
         </is>
       </c>
-      <c r="K71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R71" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="S71" s="2" t="n">
+      <c r="K72" s="13" t="n">
+        <v>1940</v>
+      </c>
+      <c r="L72" s="13" t="n">
+        <v>626</v>
+      </c>
+      <c r="M72" s="15" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="N72" s="13" t="inlineStr"/>
+      <c r="O72" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P72" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="S72" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="T71" s="2" t="inlineStr">
+      <c r="T72" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U71" s="2" t="n">
+      <c r="U72" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="2" t="inlineStr"/>
-      <c r="W71" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-20T04:21:47</t>
+      <c r="V72" s="13" t="inlineStr"/>
+      <c r="W72" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:58:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step100</t>
+        </is>
+      </c>
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-s_1701_v1</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_1701_v1</t>
+        </is>
+      </c>
+      <c r="J73" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step100</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="n">
+        <v>7547</v>
+      </c>
+      <c r="L73" s="13" t="n">
+        <v>2418</v>
+      </c>
+      <c r="M73" s="15" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="N73" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O73" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P73" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S73" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T73" s="13" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="U73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="13" t="inlineStr"/>
+      <c r="W73" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:59:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>C: long-out (max=80)</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step30_long</t>
+        </is>
+      </c>
+      <c r="H74" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step30_v3</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v3</t>
+        </is>
+      </c>
+      <c r="J74" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="n">
+        <v>2082</v>
+      </c>
+      <c r="L74" s="13" t="n">
+        <v>661</v>
+      </c>
+      <c r="M74" s="15" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="N74" s="13" t="inlineStr"/>
+      <c r="O74" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P74" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S74" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="T74" s="13" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="U74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="13" t="inlineStr"/>
+      <c r="W74" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:56:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step60</t>
+        </is>
+      </c>
+      <c r="H75" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step60_v1</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v1</t>
+        </is>
+      </c>
+      <c r="J75" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="n">
+        <v>7660</v>
+      </c>
+      <c r="L75" s="13" t="n">
+        <v>2371</v>
+      </c>
+      <c r="M75" s="15" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="N75" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O75" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P75" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S75" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T75" s="13" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="U75" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="13" t="inlineStr"/>
+      <c r="W75" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:59:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step30</t>
+        </is>
+      </c>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step30_v1</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v1</t>
+        </is>
+      </c>
+      <c r="J76" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="n">
+        <v>7807</v>
+      </c>
+      <c r="L76" s="13" t="n">
+        <v>2339</v>
+      </c>
+      <c r="M76" s="15" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="N76" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O76" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P76" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S76" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T76" s="13" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="U76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="13" t="inlineStr"/>
+      <c r="W76" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:59:00</t>
         </is>
       </c>
     </row>
@@ -7329,6 +7799,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7626,10 +8101,10 @@
         </is>
       </c>
       <c r="H6" s="18" t="n">
-        <v>7288</v>
+        <v>7845</v>
       </c>
       <c r="I6" s="19" t="n">
-        <v>0.3366</v>
+        <v>0.3374</v>
       </c>
       <c r="J6" s="18" t="inlineStr">
         <is>
@@ -7764,10 +8239,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7148</v>
+        <v>7725</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.3297</v>
+        <v>0.3309</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -7902,10 +8377,10 @@
         </is>
       </c>
       <c r="H12" s="18" t="n">
-        <v>7048</v>
+        <v>7547</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>0.3205</v>
+        <v>0.3204</v>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
@@ -8086,10 +8561,10 @@
         </is>
       </c>
       <c r="H16" s="18" t="n">
-        <v>7092</v>
+        <v>7660</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>0.3106</v>
+        <v>0.3095</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
@@ -8178,10 +8653,10 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>8092</v>
+        <v>8620</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>0.3033</v>
+        <v>0.3035</v>
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
@@ -8195,43 +8670,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D: SFT</t>
+          <t>A: base scan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Qwen2.5</t>
+          <t>Qwen3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>4B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SFT-PIPPA-r32</t>
+          <t>no-SFT (base)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r32_bo16</t>
+          <t>qwen3_4b</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8853</v>
+        <v>10577</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.3009</v>
+        <v>0.3008</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
+          <t>qwen-qwen3-4b-instruct-2507_v10</t>
         </is>
       </c>
     </row>
@@ -8241,22 +8716,22 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>A: base scan</t>
+          <t>D: SFT</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>Qwen3</t>
+          <t>Llama-3.2</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>no-SFT (base)</t>
+          <t>SFT-other</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
@@ -8266,18 +8741,18 @@
       </c>
       <c r="G20" s="18" t="inlineStr">
         <is>
-          <t>qwen3_4b</t>
+          <t>llama32_3b_anime_step100</t>
         </is>
       </c>
       <c r="H20" s="18" t="n">
-        <v>10577</v>
+        <v>8085</v>
       </c>
       <c r="I20" s="19" t="n">
         <v>0.3008</v>
       </c>
       <c r="J20" s="18" t="inlineStr">
         <is>
-          <t>qwen-qwen3-4b-instruct-2507_v10</t>
+          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8767,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Llama-3.2</t>
+          <t>Qwen2.5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8302,28 +8777,28 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SFT-other</t>
+          <t>SFT-PIPPA-r32</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step100</t>
+          <t>qwen3b_pippa_r32_bo16</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7584</v>
+        <v>9341</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.3004</v>
+        <v>0.3006</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
         </is>
       </c>
     </row>
@@ -8408,10 +8883,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>7266</v>
+        <v>7807</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.2993</v>
+        <v>0.2996</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -8500,7 +8975,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7619</v>
+        <v>8203</v>
       </c>
       <c r="I25" s="17" t="n">
         <v>0.2914</v>
@@ -8684,10 +9159,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>8104</v>
+        <v>8675</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>0.2894</v>
+        <v>0.2892</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -8730,10 +9205,10 @@
         </is>
       </c>
       <c r="H30" s="18" t="n">
-        <v>8675</v>
+        <v>9203</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>0.2881</v>
+        <v>0.2884</v>
       </c>
       <c r="J30" s="18" t="inlineStr">
         <is>
@@ -8747,43 +9222,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>D: SFT</t>
+          <t>B/C: prompt+gen</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Llama-3.2</t>
+          <t>Qwen3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>4B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SFT-other</t>
+          <t>no-SFT (base)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>B: +CoSER guide</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step30</t>
+          <t>qwen3_4b_coser_guide</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>7708</v>
+        <v>10486</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>0.2862</v>
+        <v>0.2859</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
+          <t>qwen-qwen3-4b-instruct-2507_v13</t>
         </is>
       </c>
     </row>
@@ -8793,43 +9268,43 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>B/C: prompt+gen</t>
+          <t>D: SFT</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>Qwen3</t>
+          <t>Llama-3.2</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>no-SFT (base)</t>
+          <t>SFT-other</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>B: +CoSER guide</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>qwen3_4b_coser_guide</t>
+          <t>llama32_3b_anime_step30</t>
         </is>
       </c>
       <c r="H32" s="18" t="n">
-        <v>10486</v>
+        <v>8246</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>0.2859</v>
+        <v>0.2849</v>
       </c>
       <c r="J32" s="18" t="inlineStr">
         <is>
-          <t>qwen-qwen3-4b-instruct-2507_v13</t>
+          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9455,21 +9930,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200_bo16</t>
+          <t>qwen3b_synth_step200_bo16</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10220</v>
+        <v>325</v>
       </c>
       <c r="D5" t="n">
-        <v>3034</v>
+        <v>97</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>0.2969</v>
+        <v>0.2985</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v2</t>
+          <t>zheqiwu-qwen2-5-3b-synt_99089_v1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -9486,26 +9961,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v2_step200</t>
+          <t>qwen3b_coser_step200_bo16</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3185</v>
+        <v>10220</v>
       </c>
       <c r="D6" t="n">
-        <v>902</v>
+        <v>3034</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>0.2832</v>
+        <v>0.2969</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_25179_v1</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
@@ -9517,21 +9992,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v3_gpt_step200</t>
+          <t>llama32_3b_anime_v2_step200</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2300</v>
+        <v>3698</v>
       </c>
       <c r="D7" t="n">
-        <v>637</v>
+        <v>1054</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>0.277</v>
+        <v>0.285</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_64394_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_25179_v1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -9579,21 +10054,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200</t>
+          <t>llama32_3b_anime_v3_gpt_step200</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10194</v>
+        <v>2796</v>
       </c>
       <c r="D9" t="n">
-        <v>2690</v>
+        <v>750</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>0.2639</v>
+        <v>0.2682</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_64394_v1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -9605,31 +10080,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SFT-step500</t>
+          <t>SFT-step200</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step500_bo16</t>
+          <t>qwen3b_coser_step200</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10374</v>
+        <v>10194</v>
       </c>
       <c r="D10" t="n">
-        <v>3009</v>
+        <v>2690</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>0.2901</v>
+        <v>0.2639</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_40142_v2</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -9641,26 +10116,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step500</t>
+          <t>qwen3b_coser_step500_bo16</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10286</v>
+        <v>10374</v>
       </c>
       <c r="D11" t="n">
-        <v>2721</v>
+        <v>3009</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>0.2645</v>
+        <v>0.2901</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_40142_v1</t>
+          <t>zheqiwu-qwen2-5-3b-cose_40142_v2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
@@ -9672,57 +10147,57 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step500_coser_guide</t>
+          <t>qwen3b_coser_step500</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10142</v>
+        <v>10286</v>
       </c>
       <c r="D12" t="n">
-        <v>2616</v>
+        <v>2721</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>0.2579</v>
+        <v>0.2645</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_40142_v3</t>
+          <t>zheqiwu-qwen2-5-3b-cose_40142_v1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B: +CoSER guide</t>
+          <t>default</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SFT-PIPPA-r32</t>
+          <t>SFT-step500</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r32_bo16</t>
+          <t>qwen3b_coser_step500_coser_guide</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8853</v>
+        <v>10142</v>
       </c>
       <c r="D13" t="n">
-        <v>2664</v>
+        <v>2616</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>0.3009</v>
+        <v>0.2579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
+          <t>zheqiwu-qwen2-5-3b-cose_40142_v3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>B: +CoSER guide</t>
         </is>
       </c>
     </row>
@@ -9734,57 +10209,57 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r32</t>
+          <t>qwen3b_pippa_r32_bo16</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8675</v>
+        <v>9341</v>
       </c>
       <c r="D14" t="n">
-        <v>2499</v>
+        <v>2808</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.2881</v>
+        <v>0.3006</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SFT-PIPPA-other</t>
+          <t>SFT-PIPPA-r32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r16_bo16</t>
+          <t>qwen3b_pippa_r32</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8092</v>
+        <v>9203</v>
       </c>
       <c r="D15" t="n">
-        <v>2454</v>
+        <v>2654</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>0.3033</v>
+        <v>0.2884</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r16_v2</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -9796,52 +10271,52 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r16</t>
+          <t>qwen3b_pippa_r16_bo16</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8104</v>
+        <v>8620</v>
       </c>
       <c r="D16" t="n">
-        <v>2345</v>
+        <v>2616</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.2894</v>
+        <v>0.3035</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r16_v2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SFT-other</t>
+          <t>SFT-PIPPA-other</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo64</t>
+          <t>qwen3b_pippa_r16</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1450</v>
+        <v>8675</v>
       </c>
       <c r="D17" t="n">
-        <v>532</v>
+        <v>2509</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>0.3669</v>
+        <v>0.2892</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v5</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -9858,21 +10333,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step100_long</t>
+          <t>qwen3_4b_anime_step100_bo64_long</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1448</v>
+        <v>381</v>
       </c>
       <c r="D18" t="n">
-        <v>522</v>
+        <v>150</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.3605</v>
+        <v>0.3937</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-s_1701_v2</t>
+          <t>zheqiwu-qwen3-4b-anime-s_1701_v3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -9889,26 +10364,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_long</t>
+          <t>qwen3_4b_anime_step60_bo128</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1466</v>
+        <v>376</v>
       </c>
       <c r="D19" t="n">
-        <v>524</v>
+        <v>141</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>0.3574</v>
+        <v>0.375</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v3</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C: long-out (max=80)</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -9920,21 +10395,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step30_bo32</t>
+          <t>qwen3_4b_anime_step60_bo64</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1479</v>
+        <v>2008</v>
       </c>
       <c r="D20" t="n">
-        <v>499</v>
+        <v>725</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.3374</v>
+        <v>0.3611</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v4</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9951,26 +10426,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo16</t>
+          <t>qwen3_4b_anime_step100_long</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7288</v>
+        <v>1996</v>
       </c>
       <c r="D21" t="n">
-        <v>2453</v>
+        <v>717</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>0.3366</v>
+        <v>0.3592</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v2</t>
+          <t>zheqiwu-qwen3-4b-anime-s_1701_v2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>C: long-out (max=80)</t>
         </is>
       </c>
     </row>
@@ -9982,26 +10457,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step30_bo16</t>
+          <t>qwen3_4b_anime_step60_long_freqpen</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7148</v>
+        <v>376</v>
       </c>
       <c r="D22" t="n">
-        <v>2357</v>
+        <v>131</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0.3297</v>
+        <v>0.3484</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v2</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>C: long-out (max=80)</t>
         </is>
       </c>
     </row>
@@ -10013,26 +10488,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step100</t>
+          <t>qwen3_4b_anime_step60_long</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7048</v>
+        <v>2010</v>
       </c>
       <c r="D23" t="n">
-        <v>2259</v>
+        <v>695</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>0.3205</v>
+        <v>0.3458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-s_1701_v1</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: long-out (max=80)</t>
         </is>
       </c>
     </row>
@@ -10044,26 +10519,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo32</t>
+          <t>qwen3_4b_anime_step60_bo16</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1394</v>
+        <v>7845</v>
       </c>
       <c r="D24" t="n">
-        <v>436</v>
+        <v>2647</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.3128</v>
+        <v>0.3374</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v4</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
@@ -10075,26 +10550,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60</t>
+          <t>qwen3_4b_anime_step60_bo64_tight</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7092</v>
+        <v>386</v>
       </c>
       <c r="D25" t="n">
-        <v>2203</v>
+        <v>129</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.3106</v>
+        <v>0.3342</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v1</t>
+          <t>zheqiwu-qwen3-4b-anime-s_453_v10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: conservative (T=0.8)</t>
         </is>
       </c>
     </row>
@@ -10106,26 +10581,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step30_long</t>
+          <t>qwen3_4b_anime_step60_bo64_v2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1524</v>
+        <v>425</v>
       </c>
       <c r="D26" t="n">
-        <v>469</v>
+        <v>142</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>0.3077</v>
+        <v>0.3341</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v3</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C: long-out (max=80)</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -10137,26 +10612,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v2_step100</t>
+          <t>qwen3_4b_anime_step30_bo16</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3121</v>
+        <v>7725</v>
       </c>
       <c r="D27" t="n">
-        <v>938</v>
+        <v>2556</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>0.3005</v>
+        <v>0.3309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_94942_v1</t>
+          <t>zheqiwu-qwen3-4b-anime-step30_v2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
@@ -10168,26 +10643,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step100</t>
+          <t>qwen3_4b_anime_step60_bo64_long</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7584</v>
+        <v>393</v>
       </c>
       <c r="D28" t="n">
-        <v>2278</v>
+        <v>130</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>0.3004</v>
+        <v>0.3308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: long-out (max=80)</t>
         </is>
       </c>
     </row>
@@ -10199,21 +10674,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step30</t>
+          <t>qwen3_4b_anime_step30_bo32</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7266</v>
+        <v>2026</v>
       </c>
       <c r="D29" t="n">
-        <v>2175</v>
+        <v>663</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>0.2993</v>
+        <v>0.3272</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v1</t>
+          <t>zheqiwu-qwen3-4b-anime-step30_v4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -10230,21 +10705,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v2_step300</t>
+          <t>qwen3_4b_anime_step60_bo32</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3149</v>
+        <v>1940</v>
       </c>
       <c r="D30" t="n">
-        <v>942</v>
+        <v>626</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>0.2991</v>
+        <v>0.3227</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_65099_v1</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -10261,21 +10736,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v3_gpt_step100</t>
+          <t>qwen3_4b_anime_step100</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2202</v>
+        <v>7547</v>
       </c>
       <c r="D31" t="n">
-        <v>643</v>
+        <v>2418</v>
       </c>
       <c r="E31" s="17" t="n">
-        <v>0.292</v>
+        <v>0.3204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_93952_v1</t>
+          <t>zheqiwu-qwen3-4b-anime-s_1701_v1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -10292,26 +10767,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step60</t>
+          <t>qwen3_4b_anime_step30_long</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7619</v>
+        <v>2082</v>
       </c>
       <c r="D32" t="n">
-        <v>2220</v>
+        <v>661</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.2914</v>
+        <v>0.3175</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_12275_v1</t>
+          <t>zheqiwu-qwen3-4b-anime-step30_v3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: long-out (max=80)</t>
         </is>
       </c>
     </row>
@@ -10323,21 +10798,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step30</t>
+          <t>qwen3_4b_anime_step60</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7708</v>
+        <v>7660</v>
       </c>
       <c r="D33" t="n">
-        <v>2206</v>
+        <v>2371</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>0.2862</v>
+        <v>0.3095</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -10354,21 +10829,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v3_gpt_step300</t>
+          <t>llama32_3b_anime_v2_step300</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2165</v>
+        <v>3682</v>
       </c>
       <c r="D34" t="n">
-        <v>617</v>
+        <v>1113</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>0.285</v>
+        <v>0.3023</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-ani_7262_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_65099_v1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -10385,26 +10860,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo64_tight</t>
+          <t>llama32_3b_anime_step100</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>8085</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>2432</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>0</v>
+        <v>0.3008</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-s_453_v10</t>
+          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C: conservative (T=0.8)</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -10416,26 +10891,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo64_long</t>
+          <t>qwen3_4b_anime_step30</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>7807</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2339</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0</v>
+        <v>0.2996</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v6</t>
+          <t>zheqiwu-qwen3-4b-anime-step30_v1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C: long-out (max=80)</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -10447,26 +10922,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step100_bo64_long</t>
+          <t>llama32_3b_anime_v2_step100</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>3667</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>0</v>
+        <v>0.2962</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-s_1701_v3</t>
+          <t>zheqiwu-llama-3-2-3b-an_94942_v1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C: long-out (max=80)</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -10478,26 +10953,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_long_freqpen</t>
+          <t>llama32_3b_anime_step60</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>8203</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2390</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>0.2914</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v9</t>
+          <t>zheqiwu-llama-3-2-3b-an_12275_v1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C: long-out (max=80)</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -10509,21 +10984,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo64_v2</t>
+          <t>llama32_3b_anime_v3_gpt_step100</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>2754</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>793</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>0</v>
+        <v>0.2879</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v7</t>
+          <t>zheqiwu-llama-3-2-3b-an_93952_v1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -10540,24 +11015,179 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo128</t>
+          <t>llama32_3b_anime_v3_gpt_step300</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2658</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>764</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>0</v>
+        <v>0.2874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v8</t>
+          <t>zheqiwu-llama-3-2-3b-ani_7262_v1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>qwen3b_synth_step100_bo16</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>339</v>
+      </c>
+      <c r="D41" t="n">
+        <v>97</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-synt_62780_v1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>C: best_of=16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>llama32_3b_anime_step30</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>8246</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2349</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>qwen3b_synth_step60_bo16</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>319</v>
+      </c>
+      <c r="D43" t="n">
+        <v>83</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>C: best_of=16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>qwen3b_synth_step60</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>328</v>
+      </c>
+      <c r="D44" t="n">
+        <v>85</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>qwen3b_synth_step60_bo32</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>301</v>
+      </c>
+      <c r="D45" t="n">
+        <v>74</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0.2458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>default</t>
         </is>

--- a/Onsite/submissions.xlsx
+++ b/Onsite/submissions.xlsx
@@ -3860,13 +3860,13 @@
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>3698</v>
+        <v>3986</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>1054</v>
+        <v>1130</v>
       </c>
       <c r="M36" s="15" t="n">
-        <v>0.285</v>
+        <v>0.2835</v>
       </c>
       <c r="N36" s="13" t="inlineStr"/>
       <c r="O36" s="13" t="inlineStr">
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>2796</v>
+        <v>3071</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>750</v>
+        <v>847</v>
       </c>
       <c r="M37" s="15" t="n">
-        <v>0.2682</v>
+        <v>0.2758</v>
       </c>
       <c r="N37" s="13" t="inlineStr"/>
       <c r="O37" s="13" t="inlineStr">
@@ -4029,37 +4029,41 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_synth_step200_bo16</t>
+          <t>qwen3b_coser_step200_bo16</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-synt_99089_v1</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v2</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_99089_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v2</t>
         </is>
       </c>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen2.5-3B-synth-step200</t>
+          <t>ZheqiWu/Qwen2.5-3B-CoSER-step200</t>
         </is>
       </c>
       <c r="K38" s="13" t="n">
-        <v>325</v>
+        <v>10220</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>97</v>
+        <v>3034</v>
       </c>
       <c r="M38" s="15" t="n">
-        <v>0.2985</v>
-      </c>
-      <c r="N38" s="13" t="inlineStr"/>
+        <v>0.2969</v>
+      </c>
+      <c r="N38" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O38" s="13" t="inlineStr">
         <is>
-          <t>deployed</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="P38" s="13" t="n">
@@ -4086,7 +4090,7 @@
       <c r="V38" s="13" t="inlineStr"/>
       <c r="W38" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T04:25:28</t>
+          <t>2026-06-19T21:17:02</t>
         </is>
       </c>
     </row>
@@ -4123,41 +4127,37 @@
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200_bo16</t>
+          <t>qwen3b_synth_step200_bo16</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v2</t>
+          <t>zheqiwu-qwen2-5-3b-synt_99089_v1</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-cose_30253_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_99089_v1</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen2.5-3B-CoSER-step200</t>
+          <t>ZheqiWu/Qwen2.5-3B-synth-step200</t>
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>10220</v>
+        <v>594</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>3034</v>
+        <v>176</v>
       </c>
       <c r="M39" s="15" t="n">
-        <v>0.2969</v>
-      </c>
-      <c r="N39" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2963</v>
+      </c>
+      <c r="N39" s="13" t="inlineStr"/>
       <c r="O39" s="13" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>deployed</t>
         </is>
       </c>
       <c r="P39" s="13" t="n">
@@ -4184,7 +4184,7 @@
       <c r="V39" s="13" t="inlineStr"/>
       <c r="W39" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T21:17:02</t>
+          <t>2026-06-20T04:25:28</t>
         </is>
       </c>
     </row>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="K45" s="13" t="n">
-        <v>9341</v>
+        <v>9614</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>2808</v>
+        <v>2894</v>
       </c>
       <c r="M45" s="15" t="n">
-        <v>0.3006</v>
+        <v>0.301</v>
       </c>
       <c r="N45" s="13" t="inlineStr">
         <is>
@@ -4828,13 +4828,13 @@
         </is>
       </c>
       <c r="K46" s="13" t="n">
-        <v>9203</v>
+        <v>9537</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>2654</v>
+        <v>2761</v>
       </c>
       <c r="M46" s="15" t="n">
-        <v>0.2884</v>
+        <v>0.2895</v>
       </c>
       <c r="N46" s="13" t="inlineStr">
         <is>
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="K47" s="13" t="n">
-        <v>8620</v>
+        <v>8919</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>2616</v>
+        <v>2722</v>
       </c>
       <c r="M47" s="15" t="n">
-        <v>0.3035</v>
+        <v>0.3052</v>
       </c>
       <c r="N47" s="13" t="inlineStr">
         <is>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="K48" s="13" t="n">
-        <v>8675</v>
+        <v>8943</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>2509</v>
+        <v>2586</v>
       </c>
       <c r="M48" s="15" t="n">
         <v>0.2892</v>
@@ -5103,34 +5103,38 @@
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v2_step300</t>
+          <t>llama32_3b_anime_step100</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_65099_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_65099_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_40296_v1</t>
         </is>
       </c>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Llama-3.2-3B-Anime-v2-step300</t>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-step100</t>
         </is>
       </c>
       <c r="K49" s="13" t="n">
-        <v>3682</v>
+        <v>8393</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>1113</v>
+        <v>2550</v>
       </c>
       <c r="M49" s="15" t="n">
-        <v>0.3023</v>
-      </c>
-      <c r="N49" s="13" t="inlineStr"/>
+        <v>0.3038</v>
+      </c>
+      <c r="N49" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O49" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -5160,7 +5164,7 @@
       <c r="V49" s="13" t="inlineStr"/>
       <c r="W49" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T01:28:32</t>
+          <t>2026-06-19T22:40:29</t>
         </is>
       </c>
     </row>
@@ -5197,38 +5201,34 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step100</t>
+          <t>llama32_3b_anime_v2_step300</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_65099_v1</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_40296_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_65099_v1</t>
         </is>
       </c>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Llama-3.2-3B-Anime-step100</t>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-v2-step300</t>
         </is>
       </c>
       <c r="K50" s="13" t="n">
-        <v>8085</v>
+        <v>3957</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>2432</v>
+        <v>1182</v>
       </c>
       <c r="M50" s="15" t="n">
-        <v>0.3008</v>
-      </c>
-      <c r="N50" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2987</v>
+      </c>
+      <c r="N50" s="13" t="inlineStr"/>
       <c r="O50" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -5258,7 +5258,7 @@
       <c r="V50" s="13" t="inlineStr"/>
       <c r="W50" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T22:40:29</t>
+          <t>2026-06-20T01:28:32</t>
         </is>
       </c>
     </row>
@@ -5314,13 +5314,13 @@
         </is>
       </c>
       <c r="K51" s="13" t="n">
-        <v>3667</v>
+        <v>3943</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>1086</v>
+        <v>1162</v>
       </c>
       <c r="M51" s="15" t="n">
-        <v>0.2962</v>
+        <v>0.2947</v>
       </c>
       <c r="N51" s="13" t="inlineStr"/>
       <c r="O51" s="13" t="inlineStr">
@@ -5408,13 +5408,13 @@
         </is>
       </c>
       <c r="K52" s="13" t="n">
-        <v>8203</v>
+        <v>8497</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>2390</v>
+        <v>2481</v>
       </c>
       <c r="M52" s="15" t="n">
-        <v>0.2914</v>
+        <v>0.292</v>
       </c>
       <c r="N52" s="13" t="inlineStr">
         <is>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="K53" s="13" t="n">
-        <v>2754</v>
+        <v>3057</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>793</v>
+        <v>879</v>
       </c>
       <c r="M53" s="15" t="n">
-        <v>0.2879</v>
+        <v>0.2875</v>
       </c>
       <c r="N53" s="13" t="inlineStr"/>
       <c r="O53" s="13" t="inlineStr">
@@ -5581,34 +5581,38 @@
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v3_gpt_step300</t>
+          <t>llama32_3b_anime_step30</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-ani_7262_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-ani_7262_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_23097_v1</t>
         </is>
       </c>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Llama-3.2-3B-Anime-v3-gpt-step300</t>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-step30</t>
         </is>
       </c>
       <c r="K54" s="13" t="n">
-        <v>2658</v>
+        <v>8533</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>764</v>
+        <v>2430</v>
       </c>
       <c r="M54" s="15" t="n">
-        <v>0.2874</v>
-      </c>
-      <c r="N54" s="13" t="inlineStr"/>
+        <v>0.2848</v>
+      </c>
+      <c r="N54" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O54" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -5638,7 +5642,7 @@
       <c r="V54" s="13" t="inlineStr"/>
       <c r="W54" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T02:14:06</t>
+          <t>2026-06-19T22:40:26</t>
         </is>
       </c>
     </row>
@@ -5675,38 +5679,34 @@
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step30</t>
+          <t>llama32_3b_anime_v3_gpt_step300</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
+          <t>zheqiwu-llama-3-2-3b-ani_7262_v1</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-an_23097_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-llama-3-2-3b-ani_7262_v1</t>
         </is>
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Llama-3.2-3B-Anime-step30</t>
+          <t>ZheqiWu/Llama-3.2-3B-Anime-v3-gpt-step300</t>
         </is>
       </c>
       <c r="K55" s="13" t="n">
-        <v>8246</v>
+        <v>2924</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>2349</v>
+        <v>829</v>
       </c>
       <c r="M55" s="15" t="n">
-        <v>0.2849</v>
-      </c>
-      <c r="N55" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2835</v>
+      </c>
+      <c r="N55" s="13" t="inlineStr"/>
       <c r="O55" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
@@ -5736,7 +5736,7 @@
       <c r="V55" s="13" t="inlineStr"/>
       <c r="W55" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T22:40:26</t>
+          <t>2026-06-20T02:14:06</t>
         </is>
       </c>
     </row>
@@ -5792,13 +5792,13 @@
         </is>
       </c>
       <c r="K56" s="13" t="n">
-        <v>339</v>
+        <v>631</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>97</v>
+        <v>182</v>
       </c>
       <c r="M56" s="15" t="n">
-        <v>0.2861</v>
+        <v>0.2884</v>
       </c>
       <c r="N56" s="13" t="inlineStr"/>
       <c r="O56" s="13" t="inlineStr">
@@ -5862,22 +5862,22 @@
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_synth_step60_bo16</t>
+          <t>qwen3b_synth_step60_bo32</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-synt_19065_v2</t>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v3</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_19065_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_19065_v3</t>
         </is>
       </c>
       <c r="J57" s="13" t="inlineStr">
@@ -5886,13 +5886,13 @@
         </is>
       </c>
       <c r="K57" s="13" t="n">
-        <v>319</v>
+        <v>582</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="M57" s="15" t="n">
-        <v>0.2602</v>
+        <v>0.2715</v>
       </c>
       <c r="N57" s="13" t="inlineStr"/>
       <c r="O57" s="13" t="inlineStr">
@@ -5907,7 +5907,7 @@
         <v>1</v>
       </c>
       <c r="R57" s="13" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="S57" s="13" t="n">
         <v>64</v>
@@ -5924,7 +5924,7 @@
       <c r="V57" s="13" t="inlineStr"/>
       <c r="W57" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T04:25:23</t>
+          <t>2026-06-20T04:25:25</t>
         </is>
       </c>
     </row>
@@ -5956,22 +5956,22 @@
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_synth_step60</t>
+          <t>qwen3b_synth_step60_bo16</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-synt_19065_v1</t>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v2</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_19065_v1</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_19065_v2</t>
         </is>
       </c>
       <c r="J58" s="13" t="inlineStr">
@@ -5980,13 +5980,13 @@
         </is>
       </c>
       <c r="K58" s="13" t="n">
-        <v>328</v>
+        <v>624</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="M58" s="15" t="n">
-        <v>0.2591</v>
+        <v>0.266</v>
       </c>
       <c r="N58" s="13" t="inlineStr"/>
       <c r="O58" s="13" t="inlineStr">
@@ -6001,7 +6001,7 @@
         <v>1</v>
       </c>
       <c r="R58" s="13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S58" s="13" t="n">
         <v>64</v>
@@ -6018,7 +6018,7 @@
       <c r="V58" s="13" t="inlineStr"/>
       <c r="W58" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T04:25:22</t>
+          <t>2026-06-20T04:25:23</t>
         </is>
       </c>
     </row>
@@ -6055,17 +6055,17 @@
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>qwen3b_synth_step60_bo32</t>
+          <t>qwen3b_synth_step60</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-synt_19065_v3</t>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v1</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_19065_v3</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen2-5-3b-synt_19065_v1</t>
         </is>
       </c>
       <c r="J59" s="13" t="inlineStr">
@@ -6074,13 +6074,13 @@
         </is>
       </c>
       <c r="K59" s="13" t="n">
-        <v>301</v>
+        <v>611</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="M59" s="15" t="n">
-        <v>0.2458</v>
+        <v>0.2651</v>
       </c>
       <c r="N59" s="13" t="inlineStr"/>
       <c r="O59" s="13" t="inlineStr">
@@ -6095,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="R59" s="13" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="S59" s="13" t="n">
         <v>64</v>
@@ -6112,7 +6112,7 @@
       <c r="V59" s="13" t="inlineStr"/>
       <c r="W59" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T04:25:25</t>
+          <t>2026-06-20T04:25:22</t>
         </is>
       </c>
     </row>
@@ -6168,13 +6168,13 @@
         </is>
       </c>
       <c r="K60" s="13" t="n">
-        <v>381</v>
+        <v>640</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="M60" s="15" t="n">
-        <v>0.3937</v>
+        <v>0.4031</v>
       </c>
       <c r="N60" s="13" t="inlineStr"/>
       <c r="O60" s="13" t="inlineStr">
@@ -6261,13 +6261,13 @@
         </is>
       </c>
       <c r="K61" s="13" t="n">
-        <v>376</v>
+        <v>698</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>141</v>
+        <v>256</v>
       </c>
       <c r="M61" s="15" t="n">
-        <v>0.375</v>
+        <v>0.3668</v>
       </c>
       <c r="N61" s="13" t="inlineStr"/>
       <c r="O61" s="13" t="inlineStr">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2008</v>
+        <v>2297</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>725</v>
+        <v>838</v>
       </c>
       <c r="M62" s="15" t="n">
-        <v>0.3611</v>
+        <v>0.3648</v>
       </c>
       <c r="N62" s="13" t="inlineStr"/>
       <c r="O62" s="13" t="inlineStr">
@@ -6430,32 +6430,32 @@
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step100_long</t>
+          <t>qwen3_4b_anime_step60_bo64_long</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-s_1701_v2</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v6</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_1701_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v6</t>
         </is>
       </c>
       <c r="J63" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step100</t>
+          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
         </is>
       </c>
       <c r="K63" s="13" t="n">
-        <v>1996</v>
+        <v>686</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>717</v>
+        <v>250</v>
       </c>
       <c r="M63" s="15" t="n">
-        <v>0.3592</v>
+        <v>0.3644</v>
       </c>
       <c r="N63" s="13" t="inlineStr"/>
       <c r="O63" s="13" t="inlineStr">
@@ -6470,7 +6470,7 @@
         <v>1</v>
       </c>
       <c r="R63" s="13" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="S63" s="13" t="n">
         <v>80</v>
@@ -6486,7 +6486,7 @@
       <c r="V63" s="13" t="inlineStr"/>
       <c r="W63" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T02:56:43</t>
+          <t>2026-06-20T04:21:43</t>
         </is>
       </c>
     </row>
@@ -6523,32 +6523,32 @@
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_long_freqpen</t>
+          <t>qwen3_4b_anime_step100_long</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v9</t>
+          <t>zheqiwu-qwen3-4b-anime-s_1701_v2</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v9</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_1701_v2</t>
         </is>
       </c>
       <c r="J64" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+          <t>ZheqiWu/Qwen3-4B-Anime-step100</t>
         </is>
       </c>
       <c r="K64" s="13" t="n">
-        <v>376</v>
+        <v>2273</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>131</v>
+        <v>813</v>
       </c>
       <c r="M64" s="15" t="n">
-        <v>0.3484</v>
+        <v>0.3577</v>
       </c>
       <c r="N64" s="13" t="inlineStr"/>
       <c r="O64" s="13" t="inlineStr">
@@ -6574,12 +6574,12 @@
         </is>
       </c>
       <c r="U64" s="13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="V64" s="13" t="inlineStr"/>
       <c r="W64" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T04:21:49</t>
+          <t>2026-06-20T02:56:43</t>
         </is>
       </c>
     </row>
@@ -6616,17 +6616,17 @@
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_long</t>
+          <t>qwen3_4b_anime_step60_long_freqpen</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v3</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v9</t>
         </is>
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v3</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v9</t>
         </is>
       </c>
       <c r="J65" s="13" t="inlineStr">
@@ -6635,13 +6635,13 @@
         </is>
       </c>
       <c r="K65" s="13" t="n">
-        <v>2010</v>
+        <v>649</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>695</v>
+        <v>232</v>
       </c>
       <c r="M65" s="15" t="n">
-        <v>0.3458</v>
+        <v>0.3575</v>
       </c>
       <c r="N65" s="13" t="inlineStr"/>
       <c r="O65" s="13" t="inlineStr">
@@ -6667,12 +6667,12 @@
         </is>
       </c>
       <c r="U65" s="13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="V65" s="13" t="inlineStr"/>
       <c r="W65" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T02:56:42</t>
+          <t>2026-06-20T04:21:49</t>
         </is>
       </c>
     </row>
@@ -6704,22 +6704,22 @@
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>C: conservative (T=0.8)</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo16</t>
+          <t>qwen3_4b_anime_step60_bo64_tight</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v2</t>
+          <t>zheqiwu-qwen3-4b-anime-s_453_v10</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v2</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_453_v10</t>
         </is>
       </c>
       <c r="J66" s="13" t="inlineStr">
@@ -6728,32 +6728,28 @@
         </is>
       </c>
       <c r="K66" s="13" t="n">
-        <v>7845</v>
+        <v>656</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>2647</v>
+        <v>233</v>
       </c>
       <c r="M66" s="15" t="n">
-        <v>0.3374</v>
-      </c>
-      <c r="N66" s="13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.3552</v>
+      </c>
+      <c r="N66" s="13" t="inlineStr"/>
       <c r="O66" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
         </is>
       </c>
       <c r="P66" s="13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q66" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R66" s="13" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="S66" s="13" t="n">
         <v>64</v>
@@ -6770,7 +6766,7 @@
       <c r="V66" s="13" t="inlineStr"/>
       <c r="W66" s="13" t="inlineStr">
         <is>
-          <t>2026-06-19T22:59:04</t>
+          <t>2026-06-20T04:21:50</t>
         </is>
       </c>
     </row>
@@ -6802,22 +6798,22 @@
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>C: conservative (T=0.8)</t>
+          <t>C: long-out (max=80)</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo64_tight</t>
+          <t>qwen3_4b_anime_step60_long</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-s_453_v10</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v3</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-s_453_v10</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v3</t>
         </is>
       </c>
       <c r="J67" s="13" t="inlineStr">
@@ -6826,13 +6822,13 @@
         </is>
       </c>
       <c r="K67" s="13" t="n">
-        <v>386</v>
+        <v>2296</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>129</v>
+        <v>786</v>
       </c>
       <c r="M67" s="15" t="n">
-        <v>0.3342</v>
+        <v>0.3423</v>
       </c>
       <c r="N67" s="13" t="inlineStr"/>
       <c r="O67" s="13" t="inlineStr">
@@ -6841,315 +6837,319 @@
         </is>
       </c>
       <c r="P67" s="13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q67" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R67" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S67" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="T67" s="13" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="U67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="13" t="inlineStr"/>
+      <c r="W67" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:56:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>D: SFT</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>SFT-other</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>C: best_of=16</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step60_bo16</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step60_v2</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v2</t>
+        </is>
+      </c>
+      <c r="J68" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>8107</v>
+      </c>
+      <c r="L68" s="13" t="n">
+        <v>2726</v>
+      </c>
+      <c r="M68" s="15" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="N68" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O68" s="13" t="inlineStr">
+        <is>
+          <t>deployed</t>
+        </is>
+      </c>
+      <c r="P68" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="S68" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="S67" s="13" t="n">
-        <v>64</v>
-      </c>
-      <c r="T67" s="13" t="inlineStr">
+      <c r="T68" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U67" s="13" t="n">
+      <c r="U68" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="13" t="inlineStr"/>
-      <c r="W67" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-20T04:21:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="V68" s="13" t="inlineStr"/>
+      <c r="W68" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:59:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>D: SFT</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C69" s="13" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="E68" s="13" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>SFT-other</t>
         </is>
       </c>
-      <c r="F68" s="13" t="inlineStr">
+      <c r="F69" s="13" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step60_bo64_v2</t>
-        </is>
-      </c>
-      <c r="H68" s="13" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v7</t>
-        </is>
-      </c>
-      <c r="I68" s="14" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v7</t>
-        </is>
-      </c>
-      <c r="J68" s="13" t="inlineStr">
-        <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
-        </is>
-      </c>
-      <c r="K68" s="13" t="n">
-        <v>425</v>
-      </c>
-      <c r="L68" s="13" t="n">
-        <v>142</v>
-      </c>
-      <c r="M68" s="15" t="n">
-        <v>0.3341</v>
-      </c>
-      <c r="N68" s="13" t="inlineStr"/>
-      <c r="O68" s="13" t="inlineStr">
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>qwen3_4b_anime_step30_bo32</t>
+        </is>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>zheqiwu-qwen3-4b-anime-step30_v4</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v4</t>
+        </is>
+      </c>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>2309</v>
+      </c>
+      <c r="L69" s="13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M69" s="15" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="N69" s="13" t="inlineStr"/>
+      <c r="O69" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
         </is>
       </c>
-      <c r="P68" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R68" s="13" t="n">
+      <c r="P69" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="S69" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="S68" s="13" t="n">
-        <v>64</v>
-      </c>
-      <c r="T68" s="13" t="inlineStr">
+      <c r="T69" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U68" s="13" t="n">
+      <c r="U69" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="13" t="inlineStr"/>
-      <c r="W68" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-20T04:21:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="13" t="inlineStr">
+      <c r="V69" s="13" t="inlineStr"/>
+      <c r="W69" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-20T02:58:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t>D: SFT</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="E69" s="13" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
         <is>
           <t>SFT-other</t>
         </is>
       </c>
-      <c r="F69" s="13" t="inlineStr">
+      <c r="F70" s="13" t="inlineStr">
         <is>
           <t>C: best_of=16</t>
         </is>
       </c>
-      <c r="G69" s="13" t="inlineStr">
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>qwen3_4b_anime_step30_bo16</t>
         </is>
       </c>
-      <c r="H69" s="13" t="inlineStr">
+      <c r="H70" s="13" t="inlineStr">
         <is>
           <t>zheqiwu-qwen3-4b-anime-step30_v2</t>
         </is>
       </c>
-      <c r="I69" s="14" t="inlineStr">
+      <c r="I70" s="14" t="inlineStr">
         <is>
           <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v2</t>
         </is>
       </c>
-      <c r="J69" s="13" t="inlineStr">
+      <c r="J70" s="13" t="inlineStr">
         <is>
           <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
         </is>
       </c>
-      <c r="K69" s="13" t="n">
-        <v>7725</v>
-      </c>
-      <c r="L69" s="13" t="n">
-        <v>2556</v>
-      </c>
-      <c r="M69" s="15" t="n">
-        <v>0.3309</v>
-      </c>
-      <c r="N69" s="13" t="inlineStr">
+      <c r="K70" s="13" t="n">
+        <v>8018</v>
+      </c>
+      <c r="L70" s="13" t="n">
+        <v>2647</v>
+      </c>
+      <c r="M70" s="15" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="N70" s="13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O69" s="13" t="inlineStr">
+      <c r="O70" s="13" t="inlineStr">
         <is>
           <t>deployed</t>
         </is>
       </c>
-      <c r="P69" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q69" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" s="13" t="n">
+      <c r="P70" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="S69" s="13" t="n">
+      <c r="S70" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="T69" s="13" t="inlineStr">
+      <c r="T70" s="13" t="inlineStr">
         <is>
           <t>
 </t>
         </is>
       </c>
-      <c r="U69" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" s="13" t="inlineStr"/>
-      <c r="W69" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-19T22:59:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>D: SFT</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>Qwen3</t>
-        </is>
-      </c>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="E70" s="13" t="inlineStr">
-        <is>
-          <t>SFT-other</t>
-        </is>
-      </c>
-      <c r="F70" s="13" t="inlineStr">
-        <is>
-          <t>C: long-out (max=80)</t>
-        </is>
-      </c>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>qwen3_4b_anime_step60_bo64_long</t>
-        </is>
-      </c>
-      <c r="H70" s="13" t="inlineStr">
-        <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v6</t>
-        </is>
-      </c>
-      <c r="I70" s="14" t="inlineStr">
-        <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v6</t>
-        </is>
-      </c>
-      <c r="J70" s="13" t="inlineStr">
-        <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
-        </is>
-      </c>
-      <c r="K70" s="13" t="n">
-        <v>393</v>
-      </c>
-      <c r="L70" s="13" t="n">
-        <v>130</v>
-      </c>
-      <c r="M70" s="15" t="n">
-        <v>0.3308</v>
-      </c>
-      <c r="N70" s="13" t="inlineStr"/>
-      <c r="O70" s="13" t="inlineStr">
-        <is>
-          <t>deployed</t>
-        </is>
-      </c>
-      <c r="P70" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" s="13" t="n">
-        <v>64</v>
-      </c>
-      <c r="S70" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="T70" s="13" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
       <c r="U70" s="13" t="n">
         <v>0</v>
       </c>
       <c r="V70" s="13" t="inlineStr"/>
       <c r="W70" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T04:21:43</t>
+          <t>2026-06-19T22:59:02</t>
         </is>
       </c>
     </row>
@@ -7186,32 +7186,32 @@
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step30_bo32</t>
+          <t>qwen3_4b_anime_step60_bo64_v2</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v4</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v7</t>
         </is>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step30_v4</t>
+          <t>https://console.chaiverse.com/models/zheqiwu-qwen3-4b-anime-step60_v7</t>
         </is>
       </c>
       <c r="J71" s="13" t="inlineStr">
         <is>
-          <t>ZheqiWu/Qwen3-4B-Anime-step30</t>
+          <t>ZheqiWu/Qwen3-4B-Anime-step60</t>
         </is>
       </c>
       <c r="K71" s="13" t="n">
-        <v>2026</v>
+        <v>708</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>663</v>
+        <v>233</v>
       </c>
       <c r="M71" s="15" t="n">
-        <v>0.3272</v>
+        <v>0.3291</v>
       </c>
       <c r="N71" s="13" t="inlineStr"/>
       <c r="O71" s="13" t="inlineStr">
@@ -7226,7 +7226,7 @@
         <v>1</v>
       </c>
       <c r="R71" s="13" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="S71" s="13" t="n">
         <v>64</v>
@@ -7243,7 +7243,7 @@
       <c r="V71" s="13" t="inlineStr"/>
       <c r="W71" s="13" t="inlineStr">
         <is>
-          <t>2026-06-20T02:58:36</t>
+          <t>2026-06-20T04:21:44</t>
         </is>
       </c>
     </row>
@@ -7299,13 +7299,13 @@
         </is>
       </c>
       <c r="K72" s="13" t="n">
-        <v>1940</v>
+        <v>2203</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>626</v>
+        <v>721</v>
       </c>
       <c r="M72" s="15" t="n">
-        <v>0.3227</v>
+        <v>0.3273</v>
       </c>
       <c r="N72" s="13" t="inlineStr"/>
       <c r="O72" s="13" t="inlineStr">
@@ -7393,13 +7393,13 @@
         </is>
       </c>
       <c r="K73" s="13" t="n">
-        <v>7547</v>
+        <v>7793</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>2418</v>
+        <v>2506</v>
       </c>
       <c r="M73" s="15" t="n">
-        <v>0.3204</v>
+        <v>0.3216</v>
       </c>
       <c r="N73" s="13" t="inlineStr">
         <is>
@@ -7491,13 +7491,13 @@
         </is>
       </c>
       <c r="K74" s="13" t="n">
-        <v>2082</v>
+        <v>2364</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>661</v>
+        <v>750</v>
       </c>
       <c r="M74" s="15" t="n">
-        <v>0.3175</v>
+        <v>0.3173</v>
       </c>
       <c r="N74" s="13" t="inlineStr"/>
       <c r="O74" s="13" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="K75" s="13" t="n">
-        <v>7660</v>
+        <v>7935</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>2371</v>
+        <v>2460</v>
       </c>
       <c r="M75" s="15" t="n">
-        <v>0.3095</v>
+        <v>0.31</v>
       </c>
       <c r="N75" s="13" t="inlineStr">
         <is>
@@ -7682,13 +7682,13 @@
         </is>
       </c>
       <c r="K76" s="13" t="n">
-        <v>7807</v>
+        <v>8081</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>2339</v>
+        <v>2424</v>
       </c>
       <c r="M76" s="15" t="n">
-        <v>0.2996</v>
+        <v>0.3</v>
       </c>
       <c r="N76" s="13" t="inlineStr">
         <is>
@@ -8101,10 +8101,10 @@
         </is>
       </c>
       <c r="H6" s="18" t="n">
-        <v>7845</v>
+        <v>8107</v>
       </c>
       <c r="I6" s="19" t="n">
-        <v>0.3374</v>
+        <v>0.3363</v>
       </c>
       <c r="J6" s="18" t="inlineStr">
         <is>
@@ -8239,10 +8239,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7725</v>
+        <v>8018</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.3309</v>
+        <v>0.3301</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -8302,12 +8302,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A: base scan</t>
+          <t>D: SFT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Llama-3.2</t>
+          <t>Qwen3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no-SFT (base)</t>
+          <t>SFT-other</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -8327,18 +8327,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>llama32_3b</t>
+          <t>qwen3_4b_anime_step100</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10197</v>
+        <v>7793</v>
       </c>
       <c r="I11" s="17" t="n">
         <v>0.3216</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>meta-llama-llama-3-2-3b_30223_v2</t>
+          <t>zheqiwu-qwen3-4b-anime-s_1701_v1</t>
         </is>
       </c>
     </row>
@@ -8348,12 +8348,12 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>D: SFT</t>
+          <t>A: base scan</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>Qwen3</t>
+          <t>Llama-3.2</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>SFT-other</t>
+          <t>no-SFT (base)</t>
         </is>
       </c>
       <c r="F12" s="18" t="inlineStr">
@@ -8373,18 +8373,18 @@
       </c>
       <c r="G12" s="18" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step100</t>
+          <t>llama32_3b</t>
         </is>
       </c>
       <c r="H12" s="18" t="n">
-        <v>7547</v>
+        <v>10197</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>0.3204</v>
+        <v>0.3216</v>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-s_1701_v1</t>
+          <t>meta-llama-llama-3-2-3b_30223_v2</t>
         </is>
       </c>
     </row>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="H16" s="18" t="n">
-        <v>7660</v>
+        <v>7935</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>0.3095</v>
+        <v>0.31</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>8620</v>
+        <v>8919</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>0.3035</v>
+        <v>0.3052</v>
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
@@ -8670,22 +8670,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A: base scan</t>
+          <t>D: SFT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Qwen3</t>
+          <t>Llama-3.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no-SFT (base)</t>
+          <t>SFT-other</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -8695,18 +8695,18 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>qwen3_4b</t>
+          <t>llama32_3b_anime_step100</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>10577</v>
+        <v>8393</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.3008</v>
+        <v>0.3038</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>qwen-qwen3-4b-instruct-2507_v10</t>
+          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>Llama-3.2</t>
+          <t>Qwen2.5</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
@@ -8731,28 +8731,28 @@
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>SFT-other</t>
+          <t>SFT-PIPPA-r32</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
       <c r="G20" s="18" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step100</t>
+          <t>qwen3b_pippa_r32_bo16</t>
         </is>
       </c>
       <c r="H20" s="18" t="n">
-        <v>8085</v>
+        <v>9614</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>0.3008</v>
+        <v>0.301</v>
       </c>
       <c r="J20" s="18" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
         </is>
       </c>
     </row>
@@ -8762,43 +8762,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D: SFT</t>
+          <t>A: base scan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qwen2.5</t>
+          <t>Qwen3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>4B</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SFT-PIPPA-r32</t>
+          <t>no-SFT (base)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r32_bo16</t>
+          <t>qwen3_4b</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9341</v>
+        <v>10577</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.3006</v>
+        <v>0.3008</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r32_v2</t>
+          <t>qwen-qwen3-4b-instruct-2507_v10</t>
         </is>
       </c>
     </row>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>7807</v>
+        <v>8081</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.2996</v>
+        <v>0.3</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>8203</v>
+        <v>8497</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.2914</v>
+        <v>0.292</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>B/C: prompt+gen</t>
+          <t>D: SFT</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
@@ -9099,28 +9099,28 @@
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>no-SFT (base)</t>
+          <t>SFT-PIPPA-r32</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>C: freq_penalty=0.3</t>
+          <t>default</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>qwen25_3b_freqpen</t>
+          <t>qwen3b_pippa_r32</t>
         </is>
       </c>
       <c r="H28" s="18" t="n">
-        <v>10532</v>
+        <v>9537</v>
       </c>
       <c r="I28" s="19" t="n">
-        <v>0.2894</v>
+        <v>0.2895</v>
       </c>
       <c r="J28" s="18" t="inlineStr">
         <is>
-          <t>qwen-qwen2-5-3b-instruct_v22</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D: SFT</t>
+          <t>B/C: prompt+gen</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9145,28 +9145,28 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SFT-PIPPA-other</t>
+          <t>no-SFT (base)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: freq_penalty=0.3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r16</t>
+          <t>qwen25_3b_freqpen</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>8675</v>
+        <v>10532</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>0.2892</v>
+        <v>0.2894</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
+          <t>qwen-qwen2-5-3b-instruct_v22</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>SFT-PIPPA-r32</t>
+          <t>SFT-PIPPA-other</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
@@ -9201,18 +9201,18 @@
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>qwen3b_pippa_r32</t>
+          <t>qwen3b_pippa_r16</t>
         </is>
       </c>
       <c r="H30" s="18" t="n">
-        <v>9203</v>
+        <v>8943</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>0.2884</v>
+        <v>0.2892</v>
       </c>
       <c r="J30" s="18" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-pippa-r32_v1</t>
+          <t>zheqiwu-qwen2-5-3b-pippa-r16_v1</t>
         </is>
       </c>
     </row>
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="H32" s="18" t="n">
-        <v>8246</v>
+        <v>8533</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>0.2849</v>
+        <v>0.2848</v>
       </c>
       <c r="J32" s="18" t="inlineStr">
         <is>
@@ -9930,21 +9930,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>qwen3b_synth_step200_bo16</t>
+          <t>qwen3b_coser_step200_bo16</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>325</v>
+        <v>10220</v>
       </c>
       <c r="D5" t="n">
-        <v>97</v>
+        <v>3034</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>0.2985</v>
+        <v>0.2969</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-synt_99089_v1</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -9961,21 +9961,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200_bo16</t>
+          <t>qwen3b_synth_step200_bo16</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10220</v>
+        <v>594</v>
       </c>
       <c r="D6" t="n">
-        <v>3034</v>
+        <v>176</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>0.2969</v>
+        <v>0.2963</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v2</t>
+          <t>zheqiwu-qwen2-5-3b-synt_99089_v1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -9996,13 +9996,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3698</v>
+        <v>3986</v>
       </c>
       <c r="D7" t="n">
-        <v>1054</v>
+        <v>1130</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>0.285</v>
+        <v>0.2835</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -10023,26 +10023,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>qwen3b_coser_step200_coser_guide</t>
+          <t>llama32_3b_anime_v3_gpt_step200</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10150</v>
+        <v>3071</v>
       </c>
       <c r="D8" t="n">
-        <v>2798</v>
+        <v>847</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.2757</v>
+        <v>0.2758</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-cose_30253_v3</t>
+          <t>zheqiwu-llama-3-2-3b-an_64394_v1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>B: +CoSER guide</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -10054,26 +10054,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v3_gpt_step200</t>
+          <t>qwen3b_coser_step200_coser_guide</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2796</v>
+        <v>10150</v>
       </c>
       <c r="D9" t="n">
-        <v>750</v>
+        <v>2798</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>0.2682</v>
+        <v>0.2757</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_64394_v1</t>
+          <t>zheqiwu-qwen2-5-3b-cose_30253_v3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>B: +CoSER guide</t>
         </is>
       </c>
     </row>
@@ -10213,13 +10213,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9341</v>
+        <v>9614</v>
       </c>
       <c r="D14" t="n">
-        <v>2808</v>
+        <v>2894</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.3006</v>
+        <v>0.301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -10244,13 +10244,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9203</v>
+        <v>9537</v>
       </c>
       <c r="D15" t="n">
-        <v>2654</v>
+        <v>2761</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>0.2884</v>
+        <v>0.2895</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -10275,13 +10275,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8620</v>
+        <v>8919</v>
       </c>
       <c r="D16" t="n">
-        <v>2616</v>
+        <v>2722</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.3035</v>
+        <v>0.3052</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8675</v>
+        <v>8943</v>
       </c>
       <c r="D17" t="n">
-        <v>2509</v>
+        <v>2586</v>
       </c>
       <c r="E17" s="17" t="n">
         <v>0.2892</v>
@@ -10337,13 +10337,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>381</v>
+        <v>640</v>
       </c>
       <c r="D18" t="n">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.3937</v>
+        <v>0.4031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -10368,13 +10368,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>376</v>
+        <v>698</v>
       </c>
       <c r="D19" t="n">
-        <v>141</v>
+        <v>256</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>0.375</v>
+        <v>0.3668</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -10399,13 +10399,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2008</v>
+        <v>2297</v>
       </c>
       <c r="D20" t="n">
-        <v>725</v>
+        <v>838</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.3611</v>
+        <v>0.3648</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step100_long</t>
+          <t>qwen3_4b_anime_step60_bo64_long</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1996</v>
+        <v>686</v>
       </c>
       <c r="D21" t="n">
-        <v>717</v>
+        <v>250</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>0.3592</v>
+        <v>0.3644</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-s_1701_v2</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10457,21 +10457,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_long_freqpen</t>
+          <t>qwen3_4b_anime_step100_long</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>376</v>
+        <v>2273</v>
       </c>
       <c r="D22" t="n">
-        <v>131</v>
+        <v>813</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0.3484</v>
+        <v>0.3577</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v9</t>
+          <t>zheqiwu-qwen3-4b-anime-s_1701_v2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10488,21 +10488,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_long</t>
+          <t>qwen3_4b_anime_step60_long_freqpen</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2010</v>
+        <v>649</v>
       </c>
       <c r="D23" t="n">
-        <v>695</v>
+        <v>232</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>0.3458</v>
+        <v>0.3575</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v3</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10519,26 +10519,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo16</t>
+          <t>qwen3_4b_anime_step60_bo64_tight</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7845</v>
+        <v>656</v>
       </c>
       <c r="D24" t="n">
-        <v>2647</v>
+        <v>233</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.3374</v>
+        <v>0.3552</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v2</t>
+          <t>zheqiwu-qwen3-4b-anime-s_453_v10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>C: conservative (T=0.8)</t>
         </is>
       </c>
     </row>
@@ -10550,26 +10550,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo64_tight</t>
+          <t>qwen3_4b_anime_step60_long</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>386</v>
+        <v>2296</v>
       </c>
       <c r="D25" t="n">
-        <v>129</v>
+        <v>786</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.3342</v>
+        <v>0.3423</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-s_453_v10</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C: conservative (T=0.8)</t>
+          <t>C: long-out (max=80)</t>
         </is>
       </c>
     </row>
@@ -10581,26 +10581,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo64_v2</t>
+          <t>qwen3_4b_anime_step60_bo16</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>425</v>
+        <v>8107</v>
       </c>
       <c r="D26" t="n">
-        <v>142</v>
+        <v>2726</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>0.3341</v>
+        <v>0.3363</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v7</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
@@ -10612,26 +10612,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step30_bo16</t>
+          <t>qwen3_4b_anime_step30_bo32</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7725</v>
+        <v>2309</v>
       </c>
       <c r="D27" t="n">
-        <v>2556</v>
+        <v>771</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>0.3309</v>
+        <v>0.3339</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v2</t>
+          <t>zheqiwu-qwen3-4b-anime-step30_v4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -10643,26 +10643,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step60_bo64_long</t>
+          <t>qwen3_4b_anime_step30_bo16</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>393</v>
+        <v>8018</v>
       </c>
       <c r="D28" t="n">
-        <v>130</v>
+        <v>2647</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>0.3308</v>
+        <v>0.3301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step60_v6</t>
+          <t>zheqiwu-qwen3-4b-anime-step30_v2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C: long-out (max=80)</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
@@ -10674,21 +10674,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step30_bo32</t>
+          <t>qwen3_4b_anime_step60_bo64_v2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2026</v>
+        <v>708</v>
       </c>
       <c r="D29" t="n">
-        <v>663</v>
+        <v>233</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>0.3272</v>
+        <v>0.3291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v4</t>
+          <t>zheqiwu-qwen3-4b-anime-step60_v7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -10709,13 +10709,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1940</v>
+        <v>2203</v>
       </c>
       <c r="D30" t="n">
-        <v>626</v>
+        <v>721</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>0.3227</v>
+        <v>0.3273</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -10740,13 +10740,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7547</v>
+        <v>7793</v>
       </c>
       <c r="D31" t="n">
-        <v>2418</v>
+        <v>2506</v>
       </c>
       <c r="E31" s="17" t="n">
-        <v>0.3204</v>
+        <v>0.3216</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -10771,13 +10771,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2082</v>
+        <v>2364</v>
       </c>
       <c r="D32" t="n">
-        <v>661</v>
+        <v>750</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.3175</v>
+        <v>0.3173</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -10802,13 +10802,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7660</v>
+        <v>7935</v>
       </c>
       <c r="D33" t="n">
-        <v>2371</v>
+        <v>2460</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>0.3095</v>
+        <v>0.31</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -10829,21 +10829,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v2_step300</t>
+          <t>llama32_3b_anime_step100</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3682</v>
+        <v>8393</v>
       </c>
       <c r="D34" t="n">
-        <v>1113</v>
+        <v>2550</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>0.3023</v>
+        <v>0.3038</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_65099_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -10860,21 +10860,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step100</t>
+          <t>qwen3_4b_anime_step30</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8085</v>
+        <v>8081</v>
       </c>
       <c r="D35" t="n">
-        <v>2432</v>
+        <v>2424</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>0.3008</v>
+        <v>0.3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_40296_v1</t>
+          <t>zheqiwu-qwen3-4b-anime-step30_v1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -10891,21 +10891,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>qwen3_4b_anime_step30</t>
+          <t>llama32_3b_anime_v2_step300</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7807</v>
+        <v>3957</v>
       </c>
       <c r="D36" t="n">
-        <v>2339</v>
+        <v>1182</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0.2996</v>
+        <v>0.2987</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen3-4b-anime-step30_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_65099_v1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10926,13 +10926,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3667</v>
+        <v>3943</v>
       </c>
       <c r="D37" t="n">
-        <v>1086</v>
+        <v>1162</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>0.2962</v>
+        <v>0.2947</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -10957,13 +10957,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8203</v>
+        <v>8497</v>
       </c>
       <c r="D38" t="n">
-        <v>2390</v>
+        <v>2481</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.2914</v>
+        <v>0.292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -10984,26 +10984,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v3_gpt_step100</t>
+          <t>qwen3b_synth_step100_bo16</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2754</v>
+        <v>631</v>
       </c>
       <c r="D39" t="n">
-        <v>793</v>
+        <v>182</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>0.2879</v>
+        <v>0.2884</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_93952_v1</t>
+          <t>zheqiwu-qwen2-5-3b-synt_62780_v1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
@@ -11015,21 +11015,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_v3_gpt_step300</t>
+          <t>llama32_3b_anime_v3_gpt_step100</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2658</v>
+        <v>3057</v>
       </c>
       <c r="D40" t="n">
-        <v>764</v>
+        <v>879</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>0.2874</v>
+        <v>0.2875</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-ani_7262_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_93952_v1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -11046,26 +11046,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>qwen3b_synth_step100_bo16</t>
+          <t>llama32_3b_anime_step30</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>339</v>
+        <v>8533</v>
       </c>
       <c r="D41" t="n">
-        <v>97</v>
+        <v>2430</v>
       </c>
       <c r="E41" s="17" t="n">
-        <v>0.2861</v>
+        <v>0.2848</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-synt_62780_v1</t>
+          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -11077,21 +11077,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>llama32_3b_anime_step30</t>
+          <t>llama32_3b_anime_v3_gpt_step300</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8246</v>
+        <v>2924</v>
       </c>
       <c r="D42" t="n">
-        <v>2349</v>
+        <v>829</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>0.2849</v>
+        <v>0.2835</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>zheqiwu-llama-3-2-3b-an_23097_v1</t>
+          <t>zheqiwu-llama-3-2-3b-ani_7262_v1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -11108,26 +11108,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>qwen3b_synth_step60_bo16</t>
+          <t>qwen3b_synth_step60_bo32</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>319</v>
+        <v>582</v>
       </c>
       <c r="D43" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E43" s="17" t="n">
-        <v>0.2602</v>
+        <v>0.2715</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-synt_19065_v2</t>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C: best_of=16</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -11139,26 +11139,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>qwen3b_synth_step60</t>
+          <t>qwen3b_synth_step60_bo16</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>328</v>
+        <v>624</v>
       </c>
       <c r="D44" t="n">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>0.2591</v>
+        <v>0.266</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-synt_19065_v1</t>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>C: best_of=16</t>
         </is>
       </c>
     </row>
@@ -11170,21 +11170,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>qwen3b_synth_step60_bo32</t>
+          <t>qwen3b_synth_step60</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>301</v>
+        <v>611</v>
       </c>
       <c r="D45" t="n">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>0.2458</v>
+        <v>0.2651</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>zheqiwu-qwen2-5-3b-synt_19065_v3</t>
+          <t>zheqiwu-qwen2-5-3b-synt_19065_v1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
